--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -23,6 +23,7 @@
     <sheet name="ห่วงโซ่เหตุ-ผล (ใหม่)" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="เส้น Link มีชนิด (ใหม่)" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="จัดระเบียบ+เส้นเวลา (ใหม่)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="การ์ดไอเดีย v2.7.0" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ผู้ช่วย AI (ใหม่)'!$A$1:$G$19</definedName>
@@ -3450,6 +3451,984 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>หัวข้อ</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>เงื่อนไข / ขั้นตอน</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>ผลที่คาดหวัง</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>ความสำคัญ</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>ผลทดสอบ</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>IC-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[หัวการ์ด] โครงใหม่</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>เปิดการ์ดไอเดียใน Plot Board (คลิกการ์ด)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>หัวแผงมี: เลขเฟรม #LBBN, ชื่อ, ดาว, เมนู ⋯, ปิด (✕) · ไม่มีแถบจุดสำคัญสีอำพันเต็มความกว้าง · ไม่มีแถวปุ่ม ตรวจ/คัดลอก/ลิงก์ ท้ายแผง · ไม่มีแถบฟิล์มด้านล่าง (เหลือด้านบนแถบเดียว) · แผงกว้างกว่าเดิม</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>IC-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[จุดสำคัญ] ตั้งค่าใหม่</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>การ์ดที่ยังไม่มีจุดสำคัญ → กดดาว → พิมพ์ "พระเอกชนะ" → Enter</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>มีช่องพิมพ์ใต้ชื่อทันที · หลัง Enter ดาวเป็นสีอำพันทึบ + ข้อความ "พระเอกชนะ" ใต้ชื่อ · ปิดแล้วเปิดการ์ดใหม่ ค่ายังอยู่</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>IC-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[จุดสำคัญ] แก้ / ล้าง</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>กดดาวหรือข้อความจุดสำคัญ → แก้ข้อความ Enter · แล้วกดอีกครั้ง ลบข้อความทั้งหมด Enter</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>แก้ได้ · พอลบหมด ดาวกลับเป็นเส้นโปร่ง ข้อความใต้ชื่อหาย</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IC-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[จุดสำคัญ] Esc / คลิกออก</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>กดดาว พิมพ์ค้าง → Esc · อีกครั้ง พิมพ์ค้าง → คลิกที่อื่นในแผง</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Esc = ยกเลิก ค่าเดิมคงอยู่ · คลิกออก = บันทึกค่าที่พิมพ์ · พิมพ์ Space/ลูกศรในช่อง ไม่ไปลากหรือเลื่อนกระดาน</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>IC-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[เมนู ⋯] คัดลอก + ลิงก์</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>กด ⋯ → คัดลอก · กด ⋯ → ดูรายละเอียดเต็ม</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>คัดลอก: ข้อมูลการ์ดอยู่ในคลิปบอร์ด · ดูรายละเอียดเต็ม: ไปหน้า idea ของนิยาย (รายการนี้ซ่อนถ้าไม่มี novelId)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IC-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[เมนู ⋯] ไม่ทำให้แผงปิดเอง</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>เปิดเมนู ⋯ แล้วเลือกรายการ หรือกด Esc หรือคลิกนอกเมนู</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>แผงรายละเอียดยังอยู่ (แผงปิดด้วยการคลิกนอกแผงสองครั้งติดตามกติกาเดิม)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>IC-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[ลากแผง] ปุ่มไม่เริ่มลาก</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ลากที่พื้นที่ว่าง/เลขเฟรมของหัวแผง · กดปุ่มดาว ⋯ ✕ · ดับเบิลคลิกหัวแผง</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ลากแล้วแผงย้ายตาม · กดปุ่มไม่ทำให้แผงขยับ · ดับเบิลคลิกคืนตำแหน่งเดิม</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>IC-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[หัวการ์ด] ชื่อยาว + ป้ายบรรยาย</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>เปลี่ยนชื่อไอเดียเป็นข้อความยาว ~60 ตัวอักษร · ใช้กับการ์ดโหมดบรรยาย</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ชื่อถูกตัดด้วย … · ปุ่ม ดาว ⋯ ✕ และป้าย "บรรยาย" ไม่ล้นกรอบ ไม่ทับกัน</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IC-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[หัวการ์ด] ปม + ที่มา</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>การ์ดที่ผูกปมเรื่องและมีเส้นที่มา (ancestor)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ใต้ชื่อเป็นข้อความบรรทัดเดียว (จุดสีปม · บทบาท / ไอคอนที่มา) ไม่ใช่ชิปสีเต็ม · คลิกปมเปิดสมุดปม · คลิกที่มาเปิด popover รายละเอียด มีปุ่ม "ลบการเชื่อมโยงที่มา" ใช้ได้</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IC-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[ดราม่า] กางเมื่อมีข้อมูล</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>เปิดการ์ดที่ตั้งเป้าหมาย/ขัดแย้ง/ผลลัพธ์ไว้แล้ว</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ส่วน ดราม่า กางอยู่เอง แสดงเป้าหมาย ขัดแย้ง ผลลัพธ์ (ผลลัพธ์สีตามค่า) · ชื่อหัวข้อคอลัมน์ตามประเภทฉาก เช่น เป้าหมาย/ปฏิกิริยา/Hook</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IC-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[ดราม่า] พับเมื่อว่าง</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>เปิดการ์ดที่ยังไม่ได้ตั้งดราม่าเลย</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ส่วน ดราม่า พับอยู่ เห็นหัว + "ยังไม่ได้ตั้งค่า" · กดกางแล้วมีข้อความชวนตั้งค่า</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IC-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[ดราม่า] พับ/กาง</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>กดหัว ดราม่า สลับไปมา</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ความสูงเลื่อนนุ่ม ~0.2 วินาที · ลูกศรหมุน · ตอนพับ ข้อความสรุป "เป้าหมาย → ผลลัพธ์" ขึ้นมาแทน · ตอนพับกด Tab แล้วโฟกัสไม่ไปปุ่มที่ซ่อนอยู่</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IC-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[ดราม่า] เปิดการ์ดใบอื่น</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>กางหรือพับด้วยมือ แล้วเปิดการ์ดอีกใบที่สถานะข้อมูลต่างกัน</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>สถานะพับ/กางรีเซ็ตตามข้อมูลของการ์ดใบใหม่ (มีข้อมูล = กาง, ว่าง = พับ)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IC-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>[ดราม่า] แก้แล้วอัปเดตทันที</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>กด "โครงฉาก" ในส่วนดราม่า → ตั้งเป้าหมาย/ผลลัพธ์ → บันทึก</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>popover เดิมเปิด/บันทึกได้ · ค่าในรายการและสรุปตอนพับอัปเดต ไม่ต้องปิดเปิดการ์ด</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>IC-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[Echo] ตรวจในการ์ด</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>การ์ดที่ไม่ใช่ใบแรกของฉาก ยังไม่เคยตรวจ → กด ตรวจ</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ก่อนกด: "ยังไม่ได้ตรวจ Echo Score" · ระหว่างตรวจ: ไอคอนหมุน "กำลังตรวจ…" ปุ่มกดซ้ำไม่ได้ · เสร็จ: ✓ "วิเคราะห์ Echo Score แล้ว" + badge, ปุ่มเปลี่ยนเป็น "ตรวจใหม่" · badge มุมการ์ดบน canvas ตรงกัน</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>IC-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>[Echo] การ์ดตรวจไม่ได้</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>กด ตรวจ ที่การ์ดแรกของฉาก หรือการ์ดบอร์ดโน้ต</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ขึ้นข้อความ "การ์ดนี้ตรวจไม่ได้ (การ์ดแรกของฉาก หรือเป็นบอร์ดโน้ต)"</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>IC-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>[แท็บ] เหลือ 2 แท็บ</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>เปิดการ์ดไอเดีย</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>มีแท็บ "คนในฉาก" และ "โน้ต" เท่านั้น ไม่มีเลข 01/02 กำกับ · จำนวนเป็นตัวเลขจางต่อท้ายชื่อแท็บ (ซ่อนเมื่อเป็น 0) · เปิดการ์ดใบใหม่เริ่มที่ "คนในฉาก" เสมอ</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>IC-18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>[แท็บ] เส้นใต้ + เปลี่ยนเนื้อหา</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>กดสลับแท็บไปมา</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>เส้นใต้สีอำพันเลื่อนไปแท็บที่เลือก · เนื้อหา fade เข้าพร้อมเลื่อนขึ้นเล็กน้อย ~0.2 วินาที</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IC-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>[แท็บ] ลดการเคลื่อนไหว</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>เปิด ลดการเคลื่อนไหว (reduce motion) ในระบบปฏิบัติการ แล้วลองพับดราม่า/สลับแท็บ</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ไม่มีแอนิเมชัน (สลับทันที) แต่ฟังก์ชันครบเท่าเดิม</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IC-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>[โน้ต] เขียนแบบจัดรูปแบบ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>แท็บโน้ต → เพิ่มโน้ต → พิมพ์ข้อความ ใช้ตัวหนา/เอียง/ขีดฆ่า/รายการหัวข้อย่อย/เลขลำดับ → บันทึก</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>โน้ตแสดงในรายการตามรูปแบบที่ใช้ (ตัวหนา เอียง ขีดฆ่า bullet เลข) · จำนวนโน้ตบนแท็บเพิ่ม 1</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>IC-21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>[โน้ต] @กล่าวถึงตัวละคร</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ในช่องโน้ตพิมพ์ @ → ลูกศรขึ้นลง → Enter</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>รายการแยกกลุ่ม (คำบรรยาย / ในการ์ดนี้ / ตัวละครอื่น / ตัวประกอบ) · เลือกแล้วได้ชิปชื่อ · ค้นหาด้วยนามแฝงได้ · ชื่อมีวงเล็บ/เว้นวรรคใช้ได้ · Backspace ลบชิปทั้งก้อน</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>IC-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>[โน้ต] คีย์ลัด</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>พิมพ์โน้ต → Cmd/Ctrl+Enter · อีกครั้ง พิมพ์แล้วกด Esc (ตอนรายการ @ เปิดอยู่ และตอนปิด)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Cmd/Ctrl+Enter = บันทึก (ไม่ขึ้นบรรทัดใหม่) · Esc ตอนรายการ @ เปิด = ปิดรายการอย่างเดียว · Esc ปกติ = ยกเลิก; ถ้ามีข้อความค้างต้องกดซ้ำ "ทิ้งข้อความ?"</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>IC-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>[โน้ต] โน้ตเก่า (ข้อความธรรมดา)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>เปิดการ์ดที่มีโน้ตซึ่งเขียนก่อน v2.7.0 (มี @ชื่อ ในข้อความ) → คลิกโน้ตเพื่อแก้</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>แสดงข้อความเดิมครบ · ในโหมดแก้ @ชื่อ ที่ตรงกับตัวละครกลายเป็นชิป · เปิดแล้วไม่แตะ กดยกเลิก ต้องไม่ขึ้น "ทิ้งข้อความ?"</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>IC-24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>[โน้ต] รูปแบบ บทสนทนา</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>โน้ตใหม่ เลือกรูปแบบ "บทสนทนา" → พิมพ์ "@อาร์ธอน ..." บรรทัดหนึ่ง และข้อความธรรมดาอีกบรรทัด → บันทึก</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>บรรทัดที่ขึ้นต้นด้วยชื่อ: ชื่อผู้พูดเป็นตัวอักษรสี ตัวละครเดียวกันสีเดียวกันทุกโน้ต · บรรทัดอื่นเป็นตัวเอียงสีเทา · สลับกลับ "ทั่วไป" ข้อความเหมือนเดิม</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IC-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>[โน้ต] สีของโน้ต</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>เลือกจุดสีโน้ตแต่ละสี แล้วเลือก "ทั่วไป"</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>พื้น editor เปลี่ยนตามสีที่เลือก · "ทั่วไป" = พื้นสีกลาง ไม่ใช่เหลือง · จุดหน้ารายการโน้ตตรงสีที่บันทึก</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>IC-26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>[โน้ต] แก้ / ลบ / เรียงลำดับ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>คลิกโน้ตเดิม → แก้ → อัปเดต · กด ลบ → แน่ใจ? · ลากสลับลำดับโน้ต</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>อัปเดตได้ · ลบต้องกดยืนยันสองครั้ง · ลำดับใหม่คงอยู่หลังปิดเปิดการ์ด</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>IC-27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>[โน้ต] กันปิดตอนมีโน้ตค้าง</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>พิมพ์โน้ตค้างไม่บันทึก → คลิกนอกแผงสองครั้งติด</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>แผงไม่ปิด มี toast เตือน "มีโน้ตที่ยังไม่ได้บันทึก…" · ลอง refresh/ปิดแท็บ ขึ้นกล่องยืนยันของเบราว์เซอร์</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>IC-28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>[โน้ต] โน้ตว่าง</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>เปิด editor ปล่อยว่าง หรือพิมพ์แต่เว้นวรรค/ขึ้นบรรทัดใหม่</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ปุ่ม บันทึก กดไม่ได้</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>IC-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>[คัดลอก] ข้อความโน้ต</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>มีโน้ตใหม่ (มี @ชื่อ + bullet) → ⋯ → คัดลอก → วางในที่ใดก็ได้</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ส่วน Notes เป็นข้อความอ่านรู้เรื่อง เช่น "• @ชื่อ …" ไม่มี {"ops": ...}</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>IC-30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>[ส่งออก] JSON ของฉาก</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ปุ่มส่งออกข้อมูลฉากใน Plot Board → เปิดไฟล์</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ฟิลด์ notes ของแต่ละโน้ตเป็นข้อความธรรมดา ไม่ใช่ Delta JSON</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>IC-31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>[AI] โน้ตที่ AI เห็น</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ใช้ฟีเจอร์ที่อ่านโน้ตการ์ด (ที่มา/ancestor popover, AI ที่ใช้โน้ตไอเดีย)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ข้อความโน้ตเป็นข้อความล้วน ไม่มี JSON ปน</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>IC-32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>[คนในฉาก] ฟังก์ชันเดิมครบ</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>แท็บคนในฉาก: เพิ่มผู้เข้าร่วม · ผูกชั้น (ลูกศร) · ดูเส้นเรื่อง (ไอคอนเส้นทาง) · แก้ · เอาออก · เลื่อนตัวประกอบเป็นตัวจริง</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ทุกอย่างทำงานเหมือนก่อนปรับ (ส่วนนี้ยังไม่ได้ปรับหน้าตาในรอบนี้ ยกเว้นการจัดวางใหม่ในแท็บ)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IC-33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>[Regression] ชื่อ + บรรยาย + sticky</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>คลิกชื่อเพื่อแก้ (Enter/Esc) · การ์ดโหมดบรรยาย · การ์ดที่มี sticky-note</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>แก้ชื่อได้ตามเดิม · ป้ายบรรยายแสดง · sticky-note ไม่พัง</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>IC-34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>[ธีม] สว่าง/มืด</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>สลับธีมสว่าง/มืด เปิดการ์ดทั้งสองแท็บ ดราม่ากาง/พับ</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ข้อความทุกส่วนอ่านออก คอนทราสต์พอ ไม่มีสีเหลืองจ้าในโหมดมืด</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -3457,7 +3457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4421,6 +4421,249 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>IC-35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>[แผง] หัวแผง + แท็บติดบน</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>เปิดการ์ดที่มีโน้ตหลายอัน/ยาว → เลื่อนอ่านลงล่างในแท็บโน้ต</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ดาว ⋯ ✕ และเลขเฟรม/ชื่อ ยังเห็นตลอด · แถบแท็บ คนในฉาก/โน้ต ติดบนแถบเลื่อน สลับแท็บได้โดยไม่ต้องเลื่อนกลับ · แผงไม่ล้นจอ</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>IC-36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>[โน้ต] โน้ตยาวพับได้</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>มีโน้ตที่ยาวเกิน ~6 บรรทัด</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ถูกตัดที่ ~6 บรรทัด + ปุ่ม "ดูเพิ่ม" · กดแล้วกางเต็มและปุ่มเป็น "ย่อ" · กดปุ่มไม่เปิด editor · โน้ตสั้นไม่มีปุ่ม · คลิกตัวโน้ตยังเปิดแก้ได้</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>IC-37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>[โน้ต] ปุ่มเพิ่มโน้ตอยู่บนสุด</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>แท็บโน้ต มีโน้ตหลายอัน</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ปุ่ม "+ เพิ่มโน้ต" อยู่เหนือรายการ กดแล้ว editor เปิดที่ตำแหน่งเดิม (รายการไม่ถูกดัน/ไม่กระโดด) · ระหว่างแก้โน้ตเดิม ปุ่มบนสุดไม่แสดงซ้อน</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>IC-38</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>[โน้ต] บันทึกแล้วเลื่อนไปโชว์</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>เพิ่มโน้ตใหม่ตอนรายการยาวจนโน้ตใหม่อยู่นอกจอ → บันทึก</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>โน้ตใหม่ต่อท้ายรายการ · แผงเลื่อนไปให้เห็นโน้ตนั้น + พื้นอำพันจางสั้น ๆ ~1.4 วินาที · เปิดลดการเคลื่อนไหว = เลื่อนทันที · แก้โน้ตเดิม/ลบโน้ต ไม่เลื่อน</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>IC-39</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>[โน้ต] ลำดับหลังรีเฟรช</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>เพิ่มโน้ต A แล้ว B (ในการ์ดที่ยังไม่เคยลากเรียง) → รีเฟรชหน้า → เปิดการ์ด</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>B อยู่ท้ายสุดเหมือนก่อนรีเฟรช (ลำดับคงที่) · โน้ตเก่าที่เคยเรียงไว้ไม่สลับมั่ว</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>IC-40</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>[โน้ต] ชิป @ เบาลง + จุดสี</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ดูโน้ตแบบทั่วไปที่มี @ หลายตัว · โน้ตที่ตั้งสี vs ไม่ตั้งสี</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ชื่อที่ @ เป็นตัวอักษรสีอำพันพื้นจาง ไม่ฉูดฉาด อ่านข้อความหลักง่าย · จุดสีหน้าโน้ตมีเฉพาะโน้ตที่เลือกสี</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>IC-41</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>[โน้ต] เสนอสลับเป็นบทสนทนา</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>โน้ตแบบทั่วไปที่ 2+ บรรทัดขึ้นต้นด้วย @ชื่อ → ดูใต้โน้ต → กดปุ่มเสนอ</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>มีลิงก์ "ดูเหมือนบทสนทนา — เปลี่ยนเป็นรูปแบบบทสนทนา" · กดแล้วโน้ตกลายเป็นแบบบทสนทนา (ข้อความเดิมไม่เปลี่ยน) · ไม่แสดงกับโน้ตบรรทัดเดียว/ชิปกลางประโยค/โน้ตที่เป็นบทสนทนาอยู่แล้ว</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>IC-42</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>[โน้ต] บทสนทนาแบ่งช่อง</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>โน้ตแบบบทสนทนา พิมพ์ 3–4 บรรทัดสลับ "@ผู้พูด คำพูด" กับบรรทัดไม่มี @</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ชื่อผู้พูดคอลัมน์ซ้าย คำพูดคอลัมน์ขวา เรียงแนวเดียวกันทุกบรรทัด · คำพูดยาวพับกลับในคอลัมน์ขวา ไม่ลอดใต้ชื่อ · มีเส้นบางคั่นแต่ละตา · บรรทัดไม่มี @ = บรรยายตัวเอียงเต็มความกว้าง</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>IC-43</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>[แท็บ] คีย์บอร์ด</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>โฟกัสแท็บ → ลูกศรซ้าย/ขวา, Home, End</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>สลับแท็บและโฟกัสย้ายตาม · Tab ออกจากแถบแท็บไปที่เนื้อหา (มีแท็บเดียวที่ tabindex=0)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
         </is>
       </c>
     </row>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -3457,7 +3457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>หัวแผงมี: เลขเฟรม #LBBN, ชื่อ, ดาว, เมนู ⋯, ปิด (✕) · ไม่มีแถบจุดสำคัญสีอำพันเต็มความกว้าง · ไม่มีแถวปุ่ม ตรวจ/คัดลอก/ลิงก์ ท้ายแผง · ไม่มีแถบฟิล์มด้านล่าง (เหลือด้านบนแถบเดียว) · แผงกว้างกว่าเดิม</t>
+          <t>หัวแผงมี: เลขเฟรม #LBBN, ชื่อ, ดาว, เมนู ⋯, ปิด (✕) · ไม่มีแถบจุดสำคัญสีอำพันเต็มความกว้าง · ไม่มีแถวปุ่ม ตรวจ/คัดลอก/ลิงก์ ท้ายแผง · ไม่มีแถบฟิล์มด้านล่าง (เหลือด้านบนแถบเดียว) · แผงกระชับ ~340px</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>มีโน้ตที่ยาวเกิน ~6 บรรทัด</t>
+          <t>มีโน้ตที่ยาวเกิน ~3 บรรทัด</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ถูกตัดที่ ~6 บรรทัด + ปุ่ม "ดูเพิ่ม" · กดแล้วกางเต็มและปุ่มเป็น "ย่อ" · กดปุ่มไม่เปิด editor · โน้ตสั้นไม่มีปุ่ม · คลิกตัวโน้ตยังเปิดแก้ได้</t>
+          <t>ถูกตัดที่ ~3 บรรทัด + ปุ่ม "ดูเพิ่ม" · กดแล้วกางเต็มและปุ่มเป็น "ย่อ" · กดปุ่มไม่เปิด editor · โน้ตสั้นไม่มีปุ่ม · คลิกตัวโน้ตยังเปิดแก้ได้</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4664,6 +4664,33 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>ต่ำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>IC-44</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>[ขนาด] แผงกระชับ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>เปิดการ์ดที่มีโน้ตเยอะ (5+ อัน ยาวหลายบรรทัด) บนจอ laptop</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>แผงกว้าง ~340px สูงไม่เกิน ~70% ของจอ เห็นกระดานด้านหลังชัด · ข้อความโน้ต/ดราม่า 12px อ่านออก ไม่ชิดจนอึดอัด · โน้ตยาวพับที่ 3 บรรทัด · ลากแผงไปวางไม่หลุดจอ · ชื่อยาว/ป้ายบรรยายไม่ล้นหัวแผง · toolbar editor โน้ตไม่ล้นแถว</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>สูง</t>
         </is>
       </c>
     </row>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -24,6 +24,7 @@
     <sheet name="เส้น Link มีชนิด (ใหม่)" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="จัดระเบียบ+เส้นเวลา (ใหม่)" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="การ์ดไอเดีย v2.7.0" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="เลนบนกระดาน v2.8.0" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ผู้ช่วย AI (ใหม่)'!$A$1:$G$19</definedName>
@@ -3457,7 +3458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4691,6 +4692,822 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>IC-45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>[โน้ต] รายการ @ ลอยนอกแผง</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>เปิดการ์ด → แท็บโน้ต → เพิ่มโน้ต → พิมพ์ @ (ทำตอน editor อยู่ต่ำสุดของแผง และตอนแผงเลื่อนอยู่)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>รายการชื่อลอยเหนือทุกอย่าง ไม่ถูกตัดที่ขอบแผง (ยื่นออกนอกแผงได้) · ตำแหน่งตรงใต้ตัว @ · ถ้าล่างไม่พอจะย่อความสูงให้พอดีจอ · เลือกด้วยลูกศร+Enter หรือคลิกได้ · คลิกเลือกชื่อไม่ขึ้นเตือน "มีโน้ตที่ยังไม่ได้บันทึก" และแผงไม่ปิด</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>IC-46</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>[โน้ต] Esc ตอนรายการ @ เปิด</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>พิมพ์ข้อความแล้วพิมพ์ @ ให้รายการขึ้น → กด Esc</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>รายการ @ ปิดอย่างเดียว ข้อความในโน้ตยังอยู่ editor ไม่ถูกยกเลิก · กด Esc อีกครั้ง = ยกเลิกโน้ต (มีข้อความค้างต้องกดยืนยัน)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>IC-47</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>[โน้ต] รายการ @ โหมดมืด/สว่าง</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>สลับธีมแล้วพิมพ์ @</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>พื้น/ตัวอักษรของรายการตามธีม อ่านออก แถวที่เลือกไฮไลต์ชัด หัวกลุ่ม (ในการ์ดนี้/ตัวประกอบ) แยกออก</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>IC-48</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>[การ์ด] ปุ่ม ⋮ เห็นตลอด</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ดูการ์ดบน canvas โดยไม่ชี้เมาส์ · ลองบนจอสัมผัส/โหมดจำลองมือถือ</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ปุ่ม ⋮ เห็นอยู่ตลอดทุกการ์ด (ไม่ต้อง hover) · บนจอสัมผัสปุ่มใหญ่ ~44px · กดแล้วไม่เปิดแผงรายละเอียด · ไม่ลากการ์ดโดยไม่ตั้งใจ</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>IC-49</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>[การ์ด] เมนู ⋮ แบ่งกลุ่ม</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>กด ⋮ บนการ์ด</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>หัวข้อ "เชื่อมโยง" (เชื่อมการ์ด, เชื่อมเหตุผล, ผูกปม) · "ป้ายกำกับ" (จุดสำคัญ, คำบรรยาย, Tone) · ท้ายสุด คัดลอก และ นำออกจาก canvas (สีแดง) คั่นด้วยเส้น · ทุกรายการทำงานเหมือนเดิม</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>IC-50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>[การ์ด] ไอคอนสถานะ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>การ์ดที่มีจุดสำคัญ / มีที่มา / ผูกปม / ตั้ง Tone / เป็นคำบรรยาย</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>บนการ์ดเห็นไอคอน/จุดสีของสิ่งที่ตั้งไว้ (ดาว, ที่มา, จุดสีปม, จุดสี Tone, คำบรรยาย) · การ์ดที่ไม่ตั้งอะไรไม่มีไอคอนรก</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>IC-51</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>[แผง] แถวชิปคุณสมบัติ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>เปิดการ์ดที่ยังไม่ตั้งอะไรเลย แล้วดูใต้ชื่อ</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ชิปเส้นประ 5 อัน: จุดสำคัญ, ผูกปม, ที่มา, Tone, คำบรรยาย (ชิปที่ฟีเจอร์ไม่พร้อมใช้ในบริบทนั้นไม่แสดง) · ตั้งแล้วเปลี่ยนเป็นเส้นทึบพื้นอ่อนและแสดงค่า</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>IC-52</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>[แผง] ชิปจุดสำคัญ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>กดชิป จุดสำคัญ → พิมพ์ → Enter · แก้ · ล้างข้อความ · Esc</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ตั้ง/แก้/ล้างได้ (เหมือนดาวที่หัวแผง) · ค่าสะท้อนบนการ์ดและดาวหัวแผง · ช่องพิมพ์ไม่ทำให้ Space/ลูกศรไปควบคุมกระดาน</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>IC-53</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>[แผง] ชิปปม / ที่มา</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>กด ผูกปม · กด ที่มา · การ์ดที่มีปมและที่มาแล้ว</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ผูกปม/ที่มา เปิด dialog เดิม · เมื่อมีแล้ว ชิปแสดงชื่อปม+บทบาท / ชื่อที่มา กดที่มาเปิด popover พร้อมปุ่ม "ลบการเชื่อมโยงที่มา" · มีที่มาแล้วชิป + เพิ่มที่มาเพิ่มได้</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>IC-54</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>[แผง] ชิป Tone</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>กดชิป Tone → เลือกสี → เลือกซ้ำ → ล้าง Tone</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>รายการสีเปิดใต้ชิป · เลือกแล้วชิปแสดงจุดสี+ชื่อ และการ์ดบน canvas เปลี่ยนจุดสีตาม · ล้างแล้วกลับเป็นเส้นประ</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>IC-55</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>[แผง] ชิปคำบรรยาย</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>กดชิป คำบรรยาย สลับไปมา</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>สลับสถานะได้ · ไอคอนบนการ์ดตรงกัน · ป้าย "บรรยาย" ที่หัวแผงถูกเอาออกแล้ว (ไม่ซ้ำกับชิป)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>IC-56</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>[แผง] ชิปเยอะ ไม่ล้น</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>การ์ดที่ตั้งครบทุกอย่าง + ที่มาหลายอัน + ชื่อปมยาว</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ชิปห่อเป็นหลายแถวสวย ไม่ล้นกรอบแผง · ชื่อยาวถูกตัดด้วย … · ลำดับ Tab ตามหน้าจอ</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>หัวข้อ</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>เงื่อนไข / ขั้นตอน</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>ผลที่คาดหวัง</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>ความสำคัญ</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>ผลทดสอบ</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LN-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[ชนิดเลน] เพิ่มเลนเรื่องหลัก/รอง</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>กระดานของฉาก → ปุ่ม เพิ่มเลน → เลือก เรื่องหลัก แล้วเพิ่ม เรื่องรอง</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>แสดงตัวเลือกชนิดก่อน (เรื่องหลัก/เรื่องรอง/มุมมองตัวละคร/ไทม์ไลน์/อิสระ พร้อมคำอธิบายสั้น) · เพิ่มแล้วได้ชื่อ “เรื่องหลัก” / “เรื่องรอง 1” สีไม่ซ้ำ · หัวเลนแสดงชนิด + จำนวนการ์ด</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LN-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[ชนิดเลน] POV ผูกตัวละคร</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>เพิ่มเลน → มุมมองตัวละคร → เลือกตัวละคร</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ได้เลนชื่อ “POV ชื่อตัวละคร” · หัวเลนแสดง “POV ชื่อ · n การ์ด” · ถ้านิยายไม่มีตัวละครเลย ตัวเลือก POV กดไม่ได้</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LN-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[ชนิดเลน] เปลี่ยนชนิดภายหลัง</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>หัวเลน → ⋯ → เลือกชนิดอื่น / เลือกตัวละครใต้ POV</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ชนิดเปลี่ยนตามเลือก (มีเครื่องหมายถูกที่ตัวเลือกปัจจุบัน) · เปลี่ยนจาก POV ไปชนิดอื่น ตัวละครที่ผูกถูกล้าง · ปิดแล้วเปิดกระดานใหม่ ค่ายังอยู่</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LN-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[ชนิดเลน] เลนเก่า</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>เปิดฉากที่สร้างเลนไว้ก่อน v2.8.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>เลนเก่าแสดงเป็นอิสระ (ไม่มีป้ายชนิด) ใช้งานได้ปกติ ไม่ขึ้น error · บันทึกอัตโนมัติไม่ทำให้เลนเก่าหาย</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LN-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[เมนูเลน] ปุ่ม ⋯ เห็นตลอด</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ดูหัวเลนโดยไม่ชี้เมาส์</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ปุ่ม ลูกศรพับ และ ⋯ เห็นตลอด · เมนูมี: ชนิดเลน, เลือกตัวละคร POV, เน้นเลนนี้เลน, ย้ายขึ้น/ลง, ลบเลน (แดง)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LN-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[เมนูเลน] พับ/กางเลน</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>กดลูกศรหัวเลน</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>เลนพับเหลือแถวเตี้ย ซ่อนการ์ดข้างใน · ลูกศรหมุน · กดอีกครั้งกางกลับ การ์ดอยู่ครบ · เส้นเชื่อมที่ไปหาการ์ดในเลนที่พับหายชั่วคราว กางแล้วกลับมา · ลากการ์ดอื่นมาวางเลนที่พับ ไม่ error</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LN-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[เมนูเลน] เน้นเลนนี้เลน</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>⋯ → เน้นเลนนี้เลน แล้วสลับไปเลนอื่น · เลิกเน้น</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>เลนอื่นจางลง ยังกดและลากได้ · เลิกเน้นกลับปกติ · เน้นได้ทีละเลนเดียว</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LN-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[เมนูเลน] ย้ายเลน</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>⋯ → ย้ายขึ้น / ย้ายลง · ลองเลนบนสุดและล่างสุด</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>เลนสลับตำแหน่ง · เลนบนสุดย้ายขึ้นไม่ได้ ล่างสุดย้ายลงไม่ได้ (ปุ่มจาง) · ขึ้น toast เตือนว่าเลข #LBBN เปลี่ยน · เลขการ์ดเปลี่ยนตามจริง · รีเฟรชแล้วลำดับคงอยู่</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LN-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[เมนูเลน] ลบเลน</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ลบเลนที่ยังมีการ์ด · ลบเลนสุดท้าย · ลบเลนว่าง</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>เลนที่มีการ์ด: toast ให้ย้ายการ์ดออกก่อน · เลนสุดท้ายลบไม่ได้ (ปุ่มจาง) · เลนว่างลบได้</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LN-10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[สถิติ] จำนวนการ์ด + เงียบ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>เลนที่มีการ์ดสลับห่างกัน (เช่น จังหวะ 1 และ 6) · เลนที่ไม่มีการ์ดเลย</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>หัวเลนแสดง “n การ์ด” · ช่องว่างติดกัน ≥3 จังหวะ ขึ้นข้อความอำพัน “เงียบ N จังหวะ” (ชี้ดู tooltip ช่วงจังหวะ) · เลนว่างแสดง “ยังไม่มีการ์ด” ไม่ขึ้นเงียบ · ช่องว่างสั้นกว่า 3 ไม่เตือน · เลนที่พับไม่แสดงเตือน</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LN-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[ทั่วไป] ธีม/มือถือ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>สลับธีมมืด/สว่าง · ดูกระดานบนจอแคบ</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ข้อความหัวเลนอ่านออก (สีเตือนอำพันคอนทราสต์พอ) · หัวเลนไม่ล้นกรอบ 150px แม้ชื่อยาว · ปุ่มกดได้ง่าย</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LN-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[แทร็ก] ปุ่ม S เน้นเลน</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>กดปุ่ม S ที่หัวเลนหนึ่ง แล้วกดอีกเลน · กดซ้ำเพื่อเลิก</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>เลนอื่นจางลง (ยังกดได้) · ปุ่ม S ของเลนที่เน้นเป็นสีเข้ม · เน้นได้ทีละเลน · ตรงกับตัวเลือก “เน้นเลนนี้เลน” ในเมนู ⋯</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LN-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[แทร็ก] ล็อกเลน</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>กดปุ่มกุญแจที่หัวเลน → ลองลากการ์ดในเลนนั้นออก · ลองลากการ์ดจากเลนอื่นมาวางเลนที่ล็อก · คลิกการ์ดเปิดแผงรายละเอียด</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ลากการ์ดออกจากเลนที่ล็อกไม่ได้ · วางการ์ดเข้าช่องของเลนที่ล็อกไม่ได้ (ช่องไม่ไฮไลต์) · เปิดการ์ด/แก้โน้ตได้ปกติ · ปลดล็อกแล้วลากได้ · รีเฟรชแล้วสถานะล็อกหายไป (ไม่บันทึก)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LN-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>[ซูม] แถบเลื่อนซูม</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>เลื่อนแถบ “ซูม” บนแถบเครื่องมือ 50% ถึง 120%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>กระดานย่อ/ขยายตาม ตัวเลข % อัปเดต · เส้นเชื่อมระหว่างการ์ดยังชี้ตรงกับการ์ดทุกระดับซูม · ลากการ์ดและแบ่งตอนยังทำงานถูกตำแหน่ง · ไม่แสดงบนมือถือ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LN-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[หัวอ่าน] วางที่จังหวะ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>คลิกหัวจังหวะ (เช่น จังหวะ 03) · คลิกซ้ำ · คลิกจังหวะอื่น · กดปุ่ม x ที่แถบ</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>มีเส้นตั้งสีอำพันผ่านทุกเลนที่จังหวะนั้น · หัวจังหวะไฮไลต์ · แถบด้านบนแสดง “เลน: ชื่อการ์ด” ของทุกเลนที่มีการ์ดในจังหวะนั้น · ไม่มีการ์ด = ข้อความ “ไม่มีการ์ดในจังหวะนี้” · คลิกซ้ำ/กด x ซ่อนหัวอ่าน · ใช้คีย์บอร์ด Enter/Space บนหัวจังหวะได้</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LN-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>[หัวอ่าน] ร่วมกับซูม/พับเลน</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>วางหัวอ่านแล้วซูม · พับเลนบางเลน</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>เส้นหัวอ่านยังตรงกลางคอลัมน์จังหวะเดิมทุกระดับซูม · เลนที่พับไม่แสดงการ์ดในแถบหัวอ่านผิดพลาด (หมายเหตุ: แถบนับการ์ดจากข้อมูล ไม่สนว่าพับอยู่) · ลากเลื่อนกระดานแล้วเส้นเลื่อนตาม</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>กลาง</t>
         </is>
       </c>
     </row>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -3458,7 +3458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5014,6 +5014,33 @@
         </is>
       </c>
       <c r="E57" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>IC-57</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>[การ์ด] ความสูงบน canvas</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ดูการ์ดไอเดียบนกระดานเทียบก่อน/หลัง · ลองการ์ดที่มีชื่อ/ผู้เข้าร่วมยาวหลายบรรทัด</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ไม่มีช่องว่างเปล่าระหว่างแถบฟิล์มบนกับแถวเลขการ์ด และระหว่างเนื้อหากับแถบฟิล์มล่าง · การ์ดเตี้ยลงประมาณ 20% · เส้นเชื่อมยังชี้ตรงกับการ์ด · ลาก/คลิกเปิดแผงได้ปกติ</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>กลาง</t>
         </is>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -25,6 +25,7 @@
     <sheet name="จัดระเบียบ+เส้นเวลา (ใหม่)" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="การ์ดไอเดีย v2.7.0" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="เลนบนกระดาน v2.8.0" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="รอยต่อจังหวะ v2.9.0" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ผู้ช่วย AI (ใหม่)'!$A$1:$G$19</definedName>
@@ -4875,7 +4876,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ชิปเส้นประ 5 อัน: จุดสำคัญ, ผูกปม, ที่มา, Tone, คำบรรยาย (ชิปที่ฟีเจอร์ไม่พร้อมใช้ในบริบทนั้นไม่แสดง) · ตั้งแล้วเปลี่ยนเป็นเส้นทึบพื้นอ่อนและแสดงค่า</t>
+          <t>แถวปุ่มขนาดเท่ากันแถวเดียว 5 ปุ่ม (ไอคอนบน ป้ายล่าง): จุดสำคัญ, ผูกปม, ที่มา, Tone, คำบรรยาย เส้นประ · ปุ่มที่ฟีเจอร์ไม่พร้อมใช้ในบริบทนั้นไม่แสดง และปุ่มที่เหลือแบ่งความกว้างเท่ากัน · ตั้งแล้วเปลี่ยนเป็นพื้นอ่อนเส้นทึบ · ค่าที่ตั้ง (ข้อความจุดสำคัญ, ปม, ที่มา) ขึ้นเป็นบรรทัดข้อความใต้แถวปุ่ม · ที่หัวหน้าต่างไม่มีปุ่มดาวแล้ว (เหลือ ⋯ และ ✕)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5010,7 +5011,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ชิปห่อเป็นหลายแถวสวย ไม่ล้นกรอบแผง · ชื่อยาวถูกตัดด้วย … · ลำดับ Tab ตามหน้าจอ</t>
+          <t>ปุ่มทั้ง 5 ไม่ล้น/ไม่ตัดคำในแผงกว้าง ~340px · บรรทัดค่าห่อหลายแถวสวยเมื่อมีปมยาว/ที่มาหลายอัน · ชื่อยาวถูกตัดด้วย … · ลำดับ Tab ตามหน้าจอ</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5533,6 +5534,363 @@
         </is>
       </c>
       <c r="E17" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>หัวข้อ</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>เงื่อนไข / ขั้นตอน</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>ผลที่คาดหวัง</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>ความสำคัญ</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>ผลทดสอบ</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BJ-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[รอยต่อ] จุดที่ช่องระหว่างจังหวะ</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>เปิดฉากที่มี 3+ จังหวะ ดูแถวหัวจังหวะ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>มีจุดเส้นประ “+” ที่ช่องระหว่างจังหวะ N กับ N+1 ทุกคู่ (ไม่มีที่ช่องก่อนคอลัมน์ “+” สุดท้าย) · ฉากที่มีจังหวะเดียว/ว่าง ไม่มีจุด</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BJ-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[รอยต่อ] ตั้งสี + ข้อความ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>คลิกจุด → เลือกสี → พิมพ์ข้อความ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>จุดกลายเป็นสีที่เลือก · มีแถบสีจางพาดลงผ่านทุกเลนในช่องนั้น · ข้อความแสดงใต้จุดตัดด้วย … ถ้ายาว · tooltip แสดงชื่อสี+ข้อความ · ป๊อปอัปแสดงชื่อสีและ “นับเป็นเหตุ-ผล” ถ้าติ๊กไว้</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BJ-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[รอยต่อ] แก้ / ล้าง</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>เปลี่ยนสี · ลบข้อความ · กด “ล้างการตั้งค่า”</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>เปลี่ยนสีได้ทันที · ล้างแล้วจุดกลับเป็นเส้นประ แถบสีหาย · พิมพ์ในช่องข้อความไม่ไปกดคีย์ลัดกระดาน</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BJ-04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[รอยต่อ] จำค่าหลังรีเฟรช</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ตั้งหลายรอยต่อ รอ ~2 วินาที (autosave) → รีเฟรช</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ทุกรอยต่อกลับมาตรงเดิม (สี+ข้อความ) · ฉากเก่าที่ไม่เคยตั้ง เปิดได้ปกติ ไม่มีจุดสีเอง · การ์ด/เลน/ตอนไม่หาย ไม่มีการ์ดผีโผล่</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BJ-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[รอยต่อ] ย้ายการ์ด/เพิ่มจังหวะ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ลากการ์ดไปจังหวะใหม่ท้ายสุด · ย้ายการ์ดข้ามเลน</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>รอยต่อเดิมคงตามเลขจังหวะ ไม่หลุดหรือย้ายตามการ์ด · จังหวะใหม่ได้จุดเส้นประเพิ่ม</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BJ-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[legend] ตั้งชื่อสี + ธงเหตุ-ผล</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>แถบ “การต่อจังหวะ” เหนือกระดาน → เปลี่ยนชื่อสีหนึ่ง · ล้างชื่อให้ว่างแล้วคลิกออก · ติ๊ก/เอาติ๊ก “เหตุ-ผล”</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ชื่อใหม่แสดงที่ tooltip/ป๊อปอัปด้วย · ชื่อว่างกลับเป็นชื่อเริ่มต้น · ติ๊กแล้วตัวเลข/คำเตือนเปลี่ยนทันที · รีเฟรชแล้วคงอยู่</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BJ-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[legend] ตัวนับและคำเตือน “แล้วก็…”</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ฉาก 5 จังหวะ ตั้งรอยต่อ: เหตุ→ผล, ต่อเนื่อง, (ว่าง), ตัดฉาก</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>แสดง “ยังไม่บอก 1/4” · มี “ไม่มีเหตุ-ผลติดกัน 3 รอยต่อ” (รอยต่อ 2–4) สีอำพัน · ติ๊กเหตุ-ผลที่ “ต่อเนื่อง” → คำเตือนหาย/สั้นลง</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BJ-09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[เส้นการ์ดเดิม] ซ่อน/เปิด</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ฉากที่มีเส้นการ์ดเดิม ดูกระดานครั้งแรก · กดปุ่ม “เส้นการ์ดเดิม n”</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>เส้นการ์ดเดิมถูกซ่อนเป็นค่าเริ่มต้น · ปุ่มแสดงจำนวนเส้น (ไม่แสดงถ้าไม่มีเส้น) · กดแล้วเส้นกลับมาครบ · เส้นที่มา (ancestor) ไม่ถูกซ่อน · ข้อมูลเส้นเดิมไม่หาย (รีเฟรชแล้วเปิดดูยังอยู่)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BJ-10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[ส่งออก] JSON + Markdown</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ส่งออก JSON และ Markdown ของฉากที่ตั้งรอยต่อไว้</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>JSON มี beatJoins และ joinKinds · Markdown มีหัวข้อ “การต่อจังหวะ:” เช่น “จังหวะ 1 → 2: เหตุ→ผล (เหตุ-ผล) — ข้อความ” · ฉากที่ไม่ตั้งรอยต่อ ไม่มีหัวข้อนี้</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BJ-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[วิเคราะห์] Echo ใช้รอยต่อ</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ฉากที่ตั้งรอยต่อไว้ → ใช้ตรวจ Echo Score ของการ์ดในจังหวะที่มี/ไม่มีรอยต่อเหตุ-ผลนำมา</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ผลสะท้อนว่าการ์ดจังหวะที่ถัดจากรอยต่อเหตุ-ผลนับว่ามีเหตุนำมา (badge/ผลต่างจากฉากที่ไม่ได้ตั้ง) · ฉากเก่าที่ไม่ตั้งรอยต่อ ผลเหมือนเดิม</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BJ-12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[ทั่วไป] ซูม/มืด/ผู้อ่านหน้าจอ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ซูมกระดาน 50–120% · ธีมมืด · ใช้คีย์บอร์ด Tab เข้าจุด</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>จุดและแถบอยู่ตรงช่องระหว่างจังหวะทุกระดับซูม · แถบสี/จุดอ่านออกในโหมดมืด · จุดโฟกัสด้วย Tab ได้ มี aria-label “การต่อ จังหวะ N → M: …”</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>กลาง</t>
         </is>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -5612,12 +5612,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>เปิดฉากที่มี 3+ จังหวะ ดูแถวหัวจังหวะ</t>
+          <t>เปิดฉากที่มี 3+ จังหวะ → กดปุ่ม “การต่อจังหวะ” บนแถบเครื่องมือ → ดูแถวหัวจังหวะ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>มีจุดเส้นประ “+” ที่ช่องระหว่างจังหวะ N กับ N+1 ทุกคู่ (ไม่มีที่ช่องก่อนคอลัมน์ “+” สุดท้าย) · ฉากที่มีจังหวะเดียว/ว่าง ไม่มีจุด</t>
+          <t>ก่อนกดปุ่ม: ไม่มีจุด/แถบสี/แถบชื่อสี (กระดานเหมือนเดิม) · หลังกด: มีจุดเส้นประ “+” ที่ช่องระหว่างจังหวะ N กับ N+1 ทุกคู่ (ไม่มีที่ช่องก่อนคอลัมน์ “+” สุดท้าย) และแถบชื่อสีเหนือกระดาน · ฉากที่มีจังหวะเดียว/ว่างไม่มีจุด · ฉากที่เคยตั้งรอยต่อไว้เปิดอัตโนมัติ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5796,17 +5796,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[เส้นการ์ดเดิม] ซ่อน/เปิด</t>
+          <t>[เส้นการ์ดเดิม] แสดงตามปกติ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ฉากที่มีเส้นการ์ดเดิม ดูกระดานครั้งแรก · กดปุ่ม “เส้นการ์ดเดิม n”</t>
+          <t>เปิดฉากที่มีเส้นการ์ดเดิม ดูกระดานโดยไม่แตะปุ่มใด · เปิด “การต่อจังหวะ” แล้วกดปุ่ม “เส้นการ์ดเดิม n” · ปิด “การต่อจังหวะ”</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>เส้นการ์ดเดิมถูกซ่อนเป็นค่าเริ่มต้น · ปุ่มแสดงจำนวนเส้น (ไม่แสดงถ้าไม่มีเส้น) · กดแล้วเส้นกลับมาครบ · เส้นที่มา (ancestor) ไม่ถูกซ่อน · ข้อมูลเส้นเดิมไม่หาย (รีเฟรชแล้วเปิดดูยังอยู่)</t>
+          <t>เส้นการ์ดเดิมแสดงครบเหมือน v2.8.1 · เมื่อเปิดการต่อจังหวะ มีปุ่ม “เส้นการ์ดเดิม n” สลับซ่อน/แสดงได้ · ปิดการต่อจังหวะแล้วเส้นกลับมาแสดงเสมอแม้เคยซ่อนไว้ · เส้นที่มา (ancestor) ไม่ถูกซ่อน · ข้อมูลเส้นไม่หาย</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -25,7 +25,7 @@
     <sheet name="จัดระเบียบ+เส้นเวลา (ใหม่)" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="การ์ดไอเดีย v2.7.0" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="เลนบนกระดาน v2.8.0" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="รอยต่อจังหวะ v2.9.0" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="เส้นเชื่อมสีล้วน v2.10.0" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ผู้ช่วย AI (ใหม่)'!$A$1:$G$19</definedName>
@@ -5550,7 +5550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5602,22 +5602,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BJ-01</t>
+          <t>LC-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[รอยต่อ] จุดที่ช่องระหว่างจังหวะ</t>
+          <t>[เส้น] ลากแล้วจบ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>เปิดฉากที่มี 3+ จังหวะ → กดปุ่ม “การต่อจังหวะ” บนแถบเครื่องมือ → ดูแถวหัวจังหวะ</t>
+          <t>ใช้ปุ่ม ⋮ → เชื่อมการ์ด แล้วคลิกการ์ดปลายทาง · และลากจุดเชื่อมจากการ์ดไปปล่อยที่การ์ดอื่น</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ก่อนกดปุ่ม: ไม่มีจุด/แถบสี/แถบชื่อสี (กระดานเหมือนเดิม) · หลังกด: มีจุดเส้นประ “+” ที่ช่องระหว่างจังหวะ N กับ N+1 ทุกคู่ (ไม่มีที่ช่องก่อนคอลัมน์ “+” สุดท้าย) และแถบชื่อสีเหนือกระดาน · ฉากที่มีจังหวะเดียว/ว่างไม่มีจุด · ฉากที่เคยตั้งรอยต่อไว้เปิดอัตโนมัติ</t>
+          <t>เส้นเกิดทันทีด้วยสีเริ่มต้น (แดง) · ไม่มีหน้าต่างเด้งขึ้นมาเลย · ไม่มี toast เรื่องผู้เข้าร่วม · เชื่อมซ้ำคู่เดิมแจ้ง “เชื่อมกันอยู่แล้ว”</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5629,22 +5629,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BJ-02</t>
+          <t>LC-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[รอยต่อ] ตั้งสี + ข้อความ</t>
+          <t>[เส้น] หน้าตาเส้นสีล้วน</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>คลิกจุด → เลือกสี → พิมพ์ข้อความ</t>
+          <t>ดูเส้นหลายเส้นบนกระดาน</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>จุดกลายเป็นสีที่เลือก · มีแถบสีจางพาดลงผ่านทุกเลนในช่องนั้น · ข้อความแสดงใต้จุดตัดด้วย … ถ้ายาว · tooltip แสดงชื่อสี+ข้อความ · ป๊อปอัปแสดงชื่อสีและ “นับเป็นเหตุ-ผล” ถ้าติ๊กไว้</t>
+          <t>เส้นเป็นรางสีเดียวหนา ~4px มีหัวลูกศรสีเดียวกันที่ปลายทางและจุดสีที่ต้นทาง · ไม่มีป้ายข้อความ ไม่มีรอยสไปซ์เหลือง-ดำกลางเส้น · เส้นที่มา (ancestor) ยังเป็นแถบฟิล์มแบบเดิม</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5656,103 +5656,103 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BJ-03</t>
+          <t>LC-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[รอยต่อ] แก้ / ล้าง</t>
+          <t>[เส้น] เปลี่ยนสี</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>เปลี่ยนสี · ลบข้อความ · กด “ล้างการตั้งค่า”</t>
+          <t>คลิกเส้น → เลือกสีจากจานสี · กดวงกลม + แล้วเลือกสีอื่น</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>เปลี่ยนสีได้ทันที · ล้างแล้วจุดกลับเป็นเส้นประ แถบสีหาย · พิมพ์ในช่องข้อความไม่ไปกดคีย์ลัดกระดาน</t>
+          <t>จานสี 8 สี เลือกแล้วเส้นเปลี่ยนทันทีและหน้าต่างปิด · วงกลม + เปิด color picker เลือกสีอะไรก็ได้ เปลี่ยนสดขณะเลือก และหน้าต่างยังเปิดจนกดเสร็จ · สีที่เลือกเองแสดงเป็นวงกลมสีนั้นมีขอบหนา</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>กลาง</t>
+          <t>สูง</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BJ-04</t>
+          <t>LC-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[รอยต่อ] จำค่าหลังรีเฟรช</t>
+          <t>[เส้น] จำสีล่าสุด</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ตั้งหลายรอยต่อ รอ ~2 วินาที (autosave) → รีเฟรช</t>
+          <t>เปลี่ยนเส้นหนึ่งเป็นสีเขียว แล้วลากเส้นใหม่อีกสองเส้น</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ทุกรอยต่อกลับมาตรงเดิม (สี+ข้อความ) · ฉากเก่าที่ไม่เคยตั้ง เปิดได้ปกติ ไม่มีจุดสีเอง · การ์ด/เลน/ตอนไม่หาย ไม่มีการ์ดผีโผล่</t>
+          <t>เส้นใหม่ได้สีเขียวทั้งสองเส้น (สีล่าสุดที่เลือก) · เส้นเดิมไม่เปลี่ยนสี · รีเฟรชแล้วสีของแต่ละเส้นคงอยู่ (สีล่าสุดที่จำไว้กลับเป็นแดง)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>สูง</t>
+          <t>กลาง</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BJ-05</t>
+          <t>LC-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[รอยต่อ] ย้ายการ์ด/เพิ่มจังหวะ</t>
+          <t>[เส้น] ลบเส้น</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ลากการ์ดไปจังหวะใหม่ท้ายสุด · ย้ายการ์ดข้ามเลน</t>
+          <t>คลิกเส้น → ลบเส้น</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>รอยต่อเดิมคงตามเลขจังหวะ ไม่หลุดหรือย้ายตามการ์ด · จังหวะใหม่ได้จุดเส้นประเพิ่ม</t>
+          <t>เส้นหาย toast “ลบเส้นเชื่อมแล้ว” · ผู้เข้าร่วมของการ์ดปลายทางไม่ถูกถอด (รวมถึงของที่เคยถูกคัดลอกมาจากเส้น “นำไปสู่” เก่า)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>กลาง</t>
+          <t>สูง</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BJ-06</t>
+          <t>LC-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[legend] ตั้งชื่อสี + ธงเหตุ-ผล</t>
+          <t>[เส้นเก่า] แสดงด้วยสีตามชนิดเดิม</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>แถบ “การต่อจังหวะ” เหนือกระดาน → เปลี่ยนชื่อสีหนึ่ง · ล้างชื่อให้ว่างแล้วคลิกออก · ติ๊ก/เอาติ๊ก “เหตุ-ผล”</t>
+          <t>เปิดฉากที่มีเส้นเก่าหลายชนิด</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ชื่อใหม่แสดงที่ tooltip/ป๊อปอัปด้วย · ชื่อว่างกลับเป็นชื่อเริ่มต้น · ติ๊กแล้วตัวเลข/คำเตือนเปลี่ยนทันที · รีเฟรชแล้วคงอยู่</t>
+          <t>เส้นเก่าแสดงสีตรงชนิดเดิม (นำไปสู่=เขียว, เกิดพร้อมกัน=น้ำเงิน, เกี่ยวข้อง/ขัดแย้ง=แดง) · ไม่มีป้าย “นำไปสู่” ลอยกลางเส้นอีก · รีเฟรชแล้วเส้นเก่าไม่หาย</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5764,22 +5764,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BJ-07</t>
+          <t>LC-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[legend] ตัวนับและคำเตือน “แล้วก็…”</t>
+          <t>[ผลข้างเคียง] ไม่มีเงียบ ๆ แล้ว</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ฉาก 5 จังหวะ ตั้งรอยต่อ: เหตุ→ผล, ต่อเนื่อง, (ว่าง), ตัดฉาก</t>
+          <t>เส้นเก่าชนิด “นำไปสู่”/“เกิดพร้อมกัน” → เปลี่ยนสี · ลากการ์ดปลายทางของเส้น “เกิดพร้อมกัน” ไปจังหวะอื่น</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>แสดง “ยังไม่บอก 1/4” · มี “ไม่มีเหตุ-ผลติดกัน 3 รอยต่อ” (รอยต่อ 2–4) สีอำพัน · ติ๊กเหตุ-ผลที่ “ต่อเนื่อง” → คำเตือนหาย/สั้นลง</t>
+          <t>เปลี่ยนสีไม่ก๊อปผู้เข้าร่วม ไม่ย้ายจังหวะ ไม่มี toast · การ์ดที่เคยผูกพร้อมกันลากแยกจังหวะได้อิสระ ไม่ดึงตามกัน</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5791,49 +5791,49 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BJ-09</t>
+          <t>LC-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[เส้นการ์ดเดิม] แสดงตามปกติ</t>
+          <t>[จัดเรียง] ตามทิศของเส้น</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>เปิดฉากที่มีเส้นการ์ดเดิม ดูกระดานโดยไม่แตะปุ่มใด · เปิด “การต่อจังหวะ” แล้วกดปุ่ม “เส้นการ์ดเดิม n” · ปิด “การต่อจังหวะ”</t>
+          <t>กดปุ่ม “จัดเรียงตามเส้น” บนกระดานที่มีเส้นหลายสี · กด “ย้อนกลับ” บน toast</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>เส้นการ์ดเดิมแสดงครบเหมือน v2.8.1 · เมื่อเปิดการต่อจังหวะ มีปุ่ม “เส้นการ์ดเดิม n” สลับซ่อน/แสดงได้ · ปิดการต่อจังหวะแล้วเส้นกลับมาแสดงเสมอแม้เคยซ่อนไว้ · เส้นที่มา (ancestor) ไม่ถูกซ่อน · ข้อมูลเส้นไม่หาย</t>
+          <t>การ์ดต้นทางอยู่จังหวะก่อนปลายทางตามทิศเส้นทุกเส้น (ไม่สนสี) · เลนเดิมไม่เปลี่ยน · toast “เรียงจังหวะตามทิศของเส้นเชื่อมแล้ว” · ย้อนกลับคืนตำแหน่งเดิมได้ · เส้นวนไม่ทำให้ค้าง</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>สูง</t>
+          <t>กลาง</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BJ-10</t>
+          <t>LC-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[ส่งออก] JSON + Markdown</t>
+          <t>[ส่งออก/วิเคราะห์] ไม่พัง</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ส่งออก JSON และ Markdown ของฉากที่ตั้งรอยต่อไว้</t>
+          <t>ส่งออก Markdown/JSON ของฉากที่มีเส้น · ใช้ Echo Score</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JSON มี beatJoins และ joinKinds · Markdown มีหัวข้อ “การต่อจังหวะ:” เช่น “จังหวะ 1 → 2: เหตุ→ผล (เหตุ-ผล) — ข้อความ” · ฉากที่ไม่ตั้งรอยต่อ ไม่มีหัวข้อนี้</t>
+          <t>Markdown หัวข้อ “เชื่อมไปยัง:” แสดง “- [C03] ชื่อการ์ด” (ไม่มีชื่อชนิด) · JSON มีเส้นพร้อม color · Echo ทำงานปกติ (การ์ดที่มีเส้นออกถือว่ามีเส้นเชื่อม)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5845,54 +5845,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BJ-11</t>
+          <t>LC-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[วิเคราะห์] Echo ใช้รอยต่อ</t>
+          <t>[ถอดฟีเจอร์] การต่อจังหวะหายหมด</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ฉากที่ตั้งรอยต่อไว้ → ใช้ตรวจ Echo Score ของการ์ดในจังหวะที่มี/ไม่มีรอยต่อเหตุ-ผลนำมา</t>
+          <t>เปิดกระดาน ดูแถบเครื่องมือและช่องระหว่างจังหวะ · เปิดฉากที่เคยตั้งรอยต่อไว้ (ถ้ามี) · แก้อะไรสักอย่างแล้วรอบันทึกอัตโนมัติ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ผลสะท้อนว่าการ์ดจังหวะที่ถัดจากรอยต่อเหตุ-ผลนับว่ามีเหตุนำมา (badge/ผลต่างจากฉากที่ไม่ได้ตั้ง) · ฉากเก่าที่ไม่ตั้งรอยต่อ ผลเหมือนเดิม</t>
+          <t>ไม่มีปุ่ม “การต่อจังหวะ” ไม่มีจุดวงกลม/แถบสี/แถบชื่อสี · ฉากที่เคยตั้งรอยต่อไม่มีการ์ดผี และไม่ error · หลังบันทึกอัตโนมัติ ข้อมูลรอยต่อเดิมยังอยู่ในฐานข้อมูล (ไม่ถูกลบ)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>กลาง</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>BJ-12</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>[ทั่วไป] ซูม/มืด/ผู้อ่านหน้าจอ</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ซูมกระดาน 50–120% · ธีมมืด · ใช้คีย์บอร์ด Tab เข้าจุด</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>จุดและแถบอยู่ตรงช่องระหว่างจังหวะทุกระดับซูม · แถบสี/จุดอ่านออกในโหมดมืด · จุดโฟกัสด้วย Tab ได้ มี aria-label “การต่อ จังหวะ N → M: …”</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>กลาง</t>
+          <t>สูง</t>
         </is>
       </c>
     </row>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -5550,7 +5550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5864,6 +5864,114 @@
         </is>
       </c>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LC-11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[ธีม] รางฟิล์มสี</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ดูเส้นเชื่อมหลายสี ทั้งโหมดสว่างและมืด</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>เส้นเป็นรางสีหนา ~6px มีจุดขาวเรียงกลางราง หัวลูกศรสีเดียวกันขอบเข้มบาง หมุดสี่เหลี่ยมที่ต้นทาง · จุดขาวมองเห็นทุกสี (รวมสีอ่อนเช่นเหลือง) · เส้นที่มา (ancestor) ยังเป็นแถบฟิล์มดำเดิม</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LC-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[เส้นตรง] การ์ดข้างกันสูงไม่เท่ากัน</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>การ์ดสองใบเลน/แถวเดียวกัน จังหวะติดกัน โดยใบหนึ่งชื่อผู้เข้าร่วมยาว 2 บรรทัด อีกใบ 1 บรรทัด → ลากเส้นเชื่อม</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>เส้นเป็นเส้นตรงระดับเดียวกัน ไม่มีขั้นหักเล็ก ๆ กลางทาง · ซูมหลายระดับก็ยังตรง · ย้ายการ์ดแล้วเส้นยังตรง</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LC-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[เส้นตรง] การ์ดซ้อนในจังหวะเดียวกัน</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>การ์ดสองใบซ้อนกันในช่อง/จังหวะเดียวกัน (เช่น #1031 กับ #1032) → เชื่อมใบบนไปใบล่าง และใบล่างไปใบบน</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>เส้นดิ่งสั้น ๆ จากขอบล่างใบบนลงขอบบนใบล่าง (หรือกลับกัน) มีลูกศรชัด ไม่วนออกขวาเป็นรูปตัว C · ถ้ามีการ์ดอื่นคั่นกลาง ใช้เส้นอ้อมเดิม</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LC-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>[เส้นตรง] ไม่กระทบกรณีอื่น</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>เส้นหลายเส้นรวมเข้าการ์ดเดียว / แตกจากการ์ดเดียว · เส้นข้ามหลายจังหวะ · เส้นข้ามเลน</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>บัสรวม/แตกเหมือนเดิม ไม่ทับกัน · เส้นข้ามการ์ดที่ขวางยังอ้อมไม่พาดทับ · ไม่มีเส้นหลุดออกนอกการ์ด/หัวลูกศรลอย</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>สูง</t>
         </is>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -5550,7 +5550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5972,6 +5972,33 @@
         </is>
       </c>
       <c r="E15" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LC-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>[ช่องว่าง] ถ่างเองเมื่อซ้อนมีเส้น</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>การ์ดสองใบซ้อนกันในช่องเดียว (เช่น #1031 กับ #1032) ยังไม่มีเส้น → ลากเส้นเชื่อมใบบนไปใบล่าง → ลบเส้น</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ตอนมีเส้นช่องว่างระหว่างสองใบกว้างขึ้นเอง (~24 หน่วยเพิ่ม) เส้นดิ่งและหัวลูกศรเห็นชัด ไม่อัด · ลบเส้นแล้วช่องว่างหดกลับ · การ์ดซ้อนที่ไม่มีเส้นถึงกันช่องว่างเท่าเดิม · เส้นเชื่อมทั้งกระดานยังชี้ตรงหลังความสูงเปลี่ยน · การ์ดสามใบซ้อน (A→B, B→C) ถ่างทั้งสองช่อง</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>สูง</t>
         </is>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -5550,7 +5550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5617,7 +5617,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>เส้นเกิดทันทีด้วยสีเริ่มต้น (แดง) · ไม่มีหน้าต่างเด้งขึ้นมาเลย · ไม่มี toast เรื่องผู้เข้าร่วม · เชื่อมซ้ำคู่เดิมแจ้ง “เชื่อมกันอยู่แล้ว”</t>
+          <t>เส้นเกิดทันทีด้วยสีล่าสุด (เริ่มต้นแดง) · ไม่มีหน้าต่างเด้งขึ้นมา · ถ้าการ์ดต้นทางมีผู้เข้าร่วมที่ปลายทางยังไม่มี ขึ้น toast “ส่งต่อผู้เข้าร่วม n รายการไปการ์ด …” พร้อมปุ่มย้อนกลับ · เชื่อมซ้ำคู่เดิมแจ้ง “เชื่อมกันอยู่แล้ว”</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5720,12 +5720,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>คลิกเส้น → ลบเส้น</t>
+          <t>คลิกเส้น → ลบเส้น (ทั้งเส้นที่เพิ่งลาก และเส้นเก่าที่เคยส่งต่อผู้เข้าร่วมไว้)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>เส้นหาย toast “ลบเส้นเชื่อมแล้ว” · ผู้เข้าร่วมของการ์ดปลายทางไม่ถูกถอด (รวมถึงของที่เคยถูกคัดลอกมาจากเส้น “นำไปสู่” เก่า)</t>
+          <t>เส้นหาย toast “ลบเส้นเชื่อมแล้ว” · ผู้เข้าร่วมที่เส้นนั้นส่งต่อมา (มี copiedVia) ถูกถอนออกจากการ์ดปลายทาง · ผู้เข้าร่วมที่เพิ่มเองที่ปลายทางไม่ถูกถอน</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[ผลข้างเคียง] ไม่มีเงียบ ๆ แล้ว</t>
+          <t>[ผลข้างเคียง] เปลี่ยนสีไม่ก๊อป · เกิดพร้อมกันไม่ดึงจังหวะ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>เปลี่ยนสีไม่ก๊อปผู้เข้าร่วม ไม่ย้ายจังหวะ ไม่มี toast · การ์ดที่เคยผูกพร้อมกันลากแยกจังหวะได้อิสระ ไม่ดึงตามกัน</t>
+          <t>เปลี่ยนสีไม่ก๊อปผู้เข้าร่วม ไม่ย้ายจังหวะ ไม่มี toast · การ์ดที่เคยผูกพร้อมกันลากแยกจังหวะได้อิสระ ไม่ดึงตามกัน (การส่งต่อผู้เข้าร่วมเกิดตอนลากเส้นใหม่เท่านั้น)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5999,6 +5999,60 @@
         </is>
       </c>
       <c r="E16" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LC-16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>[ส่งต่อ] ลากเส้นแล้วผู้เข้าร่วมตามไป</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>การ์ด A มีตัวละคร/ฝ่าย/ของ + สถานที่ + โน้ตแปะ การ์ด B ว่างหรือมีตัวละครบางตัวซ้ำกับ A → ลากเส้น A → B</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>B ได้ตัวละคร/ฝ่าย/ของจาก A ที่ B ยังไม่มี (ตัวซ้ำไม่ถูกเพิ่มซ้ำ) · สถานที่และโน้ตแปะไม่ถูกส่ง · บทบาทที่แก้ไว้ที่ A ติดไปด้วย · toast บอกจำนวนที่ส่งต่อ · ถ้า A ไม่มีอะไรให้ส่ง/ซ้ำหมด ไม่มี toast ส่งต่อ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LC-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>[ส่งต่อ] ปุ่มย้อนกลับ / ลบเส้น</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ลากเส้นให้ส่งต่อได้ → กด “ย้อนกลับ” บน toast · ลากใหม่แล้วคลิกเส้น → ลบเส้น · เพิ่มผู้เข้าร่วมเองที่ B ก่อนลบ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ย้อนกลับ/ลบเส้นแล้ว เส้นหายและผู้เข้าร่วมที่ส่งต่อมาถูกถอนจาก B · ผู้เข้าร่วมที่เพิ่มเองที่ B อยู่ครบ · รีเฟรชแล้วสถานะตรงกัน</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>สูง</t>
         </is>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -26,6 +26,7 @@
     <sheet name="การ์ดไอเดีย v2.7.0" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="เลนบนกระดาน v2.8.0" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="เส้นเชื่อมสีล้วน v2.10.0" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="ตรวจคำผิด v2.12.0" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ผู้ช่วย AI (ใหม่)'!$A$1:$G$19</definedName>
@@ -141,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -176,6 +177,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6646,6 +6650,588 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>หัวข้อ</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>เงื่อนไข / ขั้นตอน</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>ผลที่คาดหวัง</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>ความสำคัญ</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>ผลทดสอบ</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SC-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>[ปุ่ม] ตรวจเบื้องหลัง</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>เปิดโน้ตที่มีเนื้อหา กดปุ่ม "ตรวจคำผิด" แล้วพิมพ์ต่อในหน้าแก้ไขระหว่างรอ</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้น toast "กำลังตรวจคำผิดเบื้องหลัง — เขียนต่อได้เลย" · พิมพ์ต่อได้ไม่ค้าง · ปุ่มขึ้น "กำลังตรวจ..." จนเสร็จ · เสร็จแล้วขึ้น "ตรวจเสร็จ — พบ N จุด…" และรายการด้านขวาโหลดใหม่</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SC-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>[ปุ่ม] ไม่มีคำผิด</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>กดตรวจในโน้ตสั้น ๆ ที่สะกดถูกหมด</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้น "ตรวจเสร็จ — ไม่พบคำผิด" · รายการคำผิดเก่าของโน้ตนี้หายไป (ถูกแทนด้วยผลใหม่)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SC-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>[ปุ่ม] ใช้ข้อความล่าสุดที่ยังไม่บันทึก</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>พิมพ์ "เเพื่อน" ลงในโน้ต (ยังไม่กดบันทึก) แล้วกดตรวจ</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>รายการมี "เเพื่อน" แนะนำ "เพื่อน" — แปลว่าตรวจจากข้อความในหน้าจอ ไม่ใช่ฉบับที่บันทึกใน DB</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SC-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>[สระเบิ้ล] รูปต่าง ๆ</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>พิมพ์ "เเพื่อน ขึึ้น ไม่่้ ไไม่ น้ำำ" แล้วกดตรวจ</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ทุกคำขึ้นในรายการ คำอธิบาย "สระ/วรรณยุกต์ซ้อน — แนะนำ: …" (เพื่อน, ขึ้น, ไม้/ไม่, ไม่, น้ำ)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SC-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>[สระเบิ้ล] ลากเสียง</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>พิมพ์ในบทพูด “ว้าาาา” แล้วกดตรวจ</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้นรายการคำอธิบาย "ลากเสียงยาว ตั้งใจหรือเปล่า? — ถ้าไม่ตั้งใจ: ว้า" (แยกจากสระซ้อนทั่วไป)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SC-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>[วรรคกลางคำ] เตือน</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>พิมพ์ "เสีย งกลองดังขึ้น" แล้วกดตรวจ</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้นรายการ "เสีย ง" คำอธิบาย "เว้นวรรคกลางคำ — ควรเป็น: เสียง"</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SC-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>[วรรคกลางคำ] ไม่เตือนคำที่เว้นได้</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>พิมพ์ "ความ รู้สึก ดอก ไม้" แล้วกดตรวจ</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>ไม่มีรายการเว้นวรรคกลางคำจากสองคำนี้</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SC-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>[ปุ่มเว้นวรรค] หลายช่อง</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>พิมพ์ "เขาเดิน   ไป" (3 ช่อง) แล้วกดปุ่ม "เว้นวรรค" → กด [แก้]</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>popover ขึ้น "เว้นวรรค 3 ช่องระหว่าง … — ควรเหลือช่องเดียว" · กดแก้แล้วเหลือช่องเดียว · ขึ้นบรรทัดใหม่ติดกันหลายบรรทัดไม่ถูกเตือน</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SC-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>[ชื่อในเรื่อง] ไม่ขีด</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>ใช้ชื่อตัวละคร/สถานที่/สิ่งของ/สิ่งมีชีวิต/พลังที่บันทึกไว้ในนิยาย (เช่น เรย์กะ) ในเนื้อหา แล้วกดตรวจ</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>ชื่อที่บันทึกไว้ไม่ถูกขีด และส่วนของชื่อ (เช่น "เรย์") ก็ไม่ถูกขีด</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SC-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>[คำซ้ำหลายจุด] รวมเป็นรายการเดียว</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>ใช้คำที่ไม่มีในพจนานุกรมและไม่ได้บันทึกเป็นชื่อ (เช่น ชื่อตัวประกอบใหม่) 4 ครั้งขึ้นไปในบทเดียว แล้วกดตรวจ</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>มีรายการเดียวที่ตำแหน่งแรก คำอธิบาย "คำนี้ถูกขีด N ครั้งในบทนี้ — เป็นชื่อ/ศัพท์ในเรื่องหรือเปล่า?…" แทนการขีด N จุด</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SC-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>[ภาษาพูด] ไม่ขีด</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>พิมพ์บทพูด “ไม่อ่ะ รึเปล่า เหรอ มั้ย” แล้วกดตรวจ</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>คำภาษาพูดเหล่านี้ไม่ถูกขีด</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SC-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>[ทับศัพท์] แยกประเภท</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>พิมพ์ "กีต้าร์ อัพเดต อีเวนท์" แล้วกดตรวจ (ต้องตั้ง LONGDO_API_KEY บน Render)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้นรายการคำอธิบาย "ทับศัพท์ไม่ตรงหลักราชบัณฑิตฯ — แนะนำ: … (แก้หรือไม่ก็ได้)" · ถ้า Longdo ใช้ไม่ได้ ข้อนี้จะไม่เตือน (ข้อจำกัดที่รู้)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SC-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>[ตรวจอัตโนมัติ] เปลี่ยนสถานะ</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>เปลี่ยนสถานะโน้ตเป็น "รอพิสูจน์อักษร" แล้วรอ 1–2 นาที รีเฟรชหน้า</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>รายการคำผิดของโน้ตมีผลใหม่ และสถานะโน้ตเปลี่ยนเป็น "รอผู้เขียนตรวจ" (user_verify) · เดิมข้อนี้ไม่เคยบันทึกผล</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SC-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>[ระบบล่ม] HF ใช้ไม่ได้</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>บน Render ตั้ง SPELL_FALLBACK_URL ผิดชั่วคราว แล้วกดตรวจ</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>ยังตรวจเสร็จได้ (ใช้ผล Longdo ตรง ๆ + สระเบิ้ล/วรรคกลางคำ) · log Render มี "HF ใช้ไม่ได้ … ใช้ผล Longdo ตรง ๆ"</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SC-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>[ระบบล่ม] ล่มทั้งคู่</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>ลบ LONGDO_API_KEY และตั้ง SPELL_FALLBACK_URL ผิด แล้วกดตรวจ</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้น toast error ข้อความจากระบบ · รายการคำผิดเดิมยังอยู่ครบ (ไม่ถูกลบ)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SC-16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>[ระบบล่ม] Render restart ระหว่างตรวจ</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>กดตรวจ แล้ว restart service บน Render ทันที</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>หน้าจอขึ้น "งานตรวจหายไป (ระบบเพิ่งรีสตาร์ต) — กดตรวจใหม่อีกครั้ง" ภายในไม่กี่วินาทีหลัง service กลับมา</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SC-17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>[ปุ่ม] กดซ้ำระหว่างตรวจ</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>กดตรวจ แล้วเปิดแท็บอื่นของโน้ตเดียวกันกดตรวจซ้ำระหว่างงานแรกยังไม่เสร็จ</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>งานที่สองไม่ซ้อน (ระบบตอบว่ากำลังตรวจอยู่แล้ว) · ผลไม่ซ้ำสองชุด</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SC-18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>[ตำแหน่ง] กดคำในรายการ</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>หลังตรวจเสร็จ คลิกคำในรายการ</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>editor เลือกคำนั้นตรงตำแหน่ง ไม่กระโดดไปคำหน้าตาคล้ายกันที่อยู่ก่อนหน้า</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -6656,7 +6656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7226,6 +7226,180 @@
       </c>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SQ-01</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>[คิว] กำลังตรวจ</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>เปิดโน้ต → เปลี่ยนสถานะเป็น "รอพิสูจน์อักษร" → กลับหน้าโปรเจกต์ แท็บ "คิวแก้ไข"</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>โน้ตขึ้นบนสุดของคิว มี badge ม่วง "⟳ กำลังตรวจคำผิด…" · ตัวเลขบนแท็บนับรวมโน้ตนี้</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SQ-02</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>[คิว] เสร็จแล้วเปลี่ยนเอง</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>เปิดหน้าคิวค้างไว้หลัง SQ-01 จนตรวจเสร็จ (ไม่ต้องรีเฟรช)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>badge เปลี่ยนเป็นสีฟ้า "✓ ตรวจเสร็จ · N จุดรอดู" เอง · ภายในไม่เกิน ~30 วิหลังจากนั้นแถวย้ายไปกลุ่ม "รอตรวจสอบ" ปุ่มเป็น "ดูผลตรวจ"</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SQ-03</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>[คิว] จำนวนจุด</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>โน้ตสถานะ "รอตรวจสอบ" ที่มีคำผิด → เข้าไปกด resolve บางรายการ → กลับมาหน้าคิว</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>ตัวเลข "N จุดรอดู" ลดลงตามจำนวนที่ resolve · ถ้า resolve หมดขึ้น "ตรวจเสร็จ · ไม่พบคำผิด"</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SQ-04</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>[คิว] งานหาย</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>สั่งตรวจ (SQ-01) แล้ว restart service บน Render ระหว่างตรวจ</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>badge เหลือง "งานตรวจหาย (ระบบรีสตาร์ต)" + ปุ่ม "ตรวจใหม่" · กดแล้วกลับเป็น "กำลังตรวจคำผิด…"</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SQ-05</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>[คิว] ลำดับ</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>มีโน้ตทั้ง 3 สถานะ (รอพิสูจน์อักษร / รอตรวจสอบ / รอ Rewrite)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>เรียง: กำลังตรวจ → ตรวจเสร็จรอดู → รอ Rewrite · แถว "รอ Rewrite" ไม่มี badge และปุ่มยังเป็น "ตรวจแก้ (Rewrite)"</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SQ-06</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>[คิว] ว่าง</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>ไม่มีโน้ตในสามสถานะนี้</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้น "ไม่มีงานในคิว" พร้อมข้อความแนะนำให้ตั้งสถานะรอพิสูจน์อักษรหรือรอ Rewrite</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -6656,7 +6656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7400,6 +7400,238 @@
       </c>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SR-01</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>[รอ Rewrite] ตรวจอัตโนมัติ</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>ตอนที่ไม่เคยตรวจคำผิด → ตั้งสถานะ "รอ Rewrite"</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้น toast "เริ่มตรวจคำผิดเบื้องหลัง…" ไม่มีหน้าต่างถาม · ในคิว แถวนั้นขึ้น "⟳ กำลังตรวจคำผิด…" แล้วกลายเป็น "N จุดคำผิดค้าง" · สถานะยังเป็นรอ Rewrite</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SR-02</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>[รอ Rewrite] เคยตรวจแล้ว → ถาม</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>ตอนที่มีผลตรวจคำผิดอยู่แล้ว → ตั้งสถานะ "รอ Rewrite" (หรือรอพิสูจน์อักษร) อีกครั้ง</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้นหน้าต่างถาม "ตอนนี้ตรวจคำผิดไว้แล้ว (N รายการ) ตรวจใหม่ไหม?…" · กดยกเลิก = สถานะเปลี่ยนแต่ไม่ตรวจ ผลเดิมอยู่ครบ · กดตกลง = ตรวจใหม่ ผลเดิมถูกแทนที่</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SR-03</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>[รอพิสูจน์อักษร] ยังเปลี่ยนสถานะตอนเสร็จ</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>ตั้งสถานะ "รอพิสูจน์อักษร" ตอนที่ไม่เคยตรวจ</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>ตรวจเสร็จแล้วสถานะเปลี่ยนเป็น "รอตรวจสอบ" เหมือนเดิม (ต่างจากรอ Rewrite ที่คงสถานะ)</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SR-04</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>[ตรวจทั้งคิว] บางตอนเคยตรวจ</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>คิวมีทั้งตอนที่เคยและไม่เคยตรวจ → กด "ตรวจคำผิดทั้งคิว" → กดยกเลิกในหน้าต่างถาม</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>ตรวจเฉพาะตอนที่ยังไม่เคยตรวจ ทีละตอน · toast ขึ้น "ตรวจทั้งคิว i/N — ชื่อตอน" · badge ของตอนที่กำลังตรวจหมุน · เสร็จแล้ว "ตรวจทั้งคิวเสร็จ — สำเร็จ X ตอน"</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SR-05</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>[ตรวจทั้งคิว] ตรวจใหม่ทั้งหมด</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>กด "ตรวจคำผิดทั้งคิว" → กดตกลงในหน้าต่างถาม</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>ตรวจทุกตอนในคิว ผลเดิมของตอนที่เคยตรวจถูกแทนที่</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SR-06</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>[ตรวจทั้งคิว] หยุดกลางทาง</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>ระหว่างตรวจทั้งคิว กด "หยุดตรวจทั้งคิว"</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>ตอนที่กำลังตรวจอยู่ตรวจต่อจนเสร็จ แต่ไม่เริ่มตอนถัดไป · toast "ตรวจทั้งคิวเสร็จ (หยุดกลางทาง)…"</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>SR-07</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>[ตรวจทั้งคิว] ตรวจครบแล้ว</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>ทุกตอนในคิวเคยตรวจ → กดตรวจทั้งคิว → กดยกเลิก</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้น "ทุกตอนในคิวตรวจไว้แล้ว" ไม่มีการตรวจ</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>SR-08</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>[ตรวจทั้งคิว] ตอนว่าง</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>คิวมีตอนที่ไม่มีเนื้อหา</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>ตอนนั้นนับเป็น "ไม่สำเร็จ" ในสรุป แล้วตรวจตอนถัดไปต่อ</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -6656,7 +6656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ขึ้นหน้าต่างถาม "ตอนนี้ตรวจคำผิดไว้แล้ว (N รายการ) ตรวจใหม่ไหม?…" · กดยกเลิก = สถานะเปลี่ยนแต่ไม่ตรวจ ผลเดิมอยู่ครบ · กดตกลง = ตรวจใหม่ ผลเดิมถูกแทนที่</t>
+          <t>ขึ้นหน้าต่างของแอป (เข้าธีม ไม่ใช่ป๊อปอัปเบราว์เซอร์) "ตอนนี้ตรวจคำผิดไว้แล้ว · มีผลตรวจเดิม N รายการ" ปุ่ม [ไม่ต้องตรวจ] [ตรวจใหม่] · ไม่ต้องตรวจ = สถานะเปลี่ยนแต่ผลเดิมอยู่ครบ · ตรวจใหม่ = ผลเดิมถูกแทนที่</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>คิวมีทั้งตอนที่เคยและไม่เคยตรวจ → กด "ตรวจคำผิดทั้งคิว" → กดยกเลิกในหน้าต่างถาม</t>
+          <t>คิวมีทั้งตอนที่เคยและไม่เคยตรวจ → กด "ตรวจคำผิดทั้งคิว" → เลือก "เฉพาะที่ยังไม่ตรวจ (N)"</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>ตรวจเฉพาะตอนที่ยังไม่เคยตรวจ ทีละตอน · toast ขึ้น "ตรวจทั้งคิว i/N — ชื่อตอน" · badge ของตอนที่กำลังตรวจหมุน · เสร็จแล้ว "ตรวจทั้งคิวเสร็จ — สำเร็จ X ตอน"</t>
+          <t>toast "ส่ง N ตอนเข้าคิวตรวจแล้ว" · ปุ่มเปลี่ยนเป็นแผงม่วง "ตรวจคำผิด x/N ตอน · อีกราว M นาที / กำลังตรวจ: ชื่อตอน · รอคิว K ตอน" · badge ของแต่ละตอนขึ้น "รอคิวตรวจ #n" หรือ "กำลังตรวจคำผิด…" · ครบแล้ว toast "ตรวจคำผิดทั้งคิวเสร็จแล้ว" แผงกลับเป็นปุ่ม</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -7530,7 +7530,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>กด "ตรวจคำผิดทั้งคิว" → กดตกลงในหน้าต่างถาม</t>
+          <t>กด "ตรวจคำผิดทั้งคิว" → เลือก "ตรวจใหม่ทุกตอน (N)"</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>ระหว่างตรวจทั้งคิว กด "หยุดตรวจทั้งคิว"</t>
+          <t>ระหว่างตรวจทั้งคิว กด "หยุดที่เหลือ" ในแผง</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>ตอนที่กำลังตรวจอยู่ตรวจต่อจนเสร็จ แต่ไม่เริ่มตอนถัดไป · toast "ตรวจทั้งคิวเสร็จ (หยุดกลางทาง)…"</t>
+          <t>toast "ถอน K ตอนออกจากคิว…" · ตอนที่กำลังตรวจตรวจต่อจนเสร็จ ตอนที่รอคิวไม่ถูกตรวจ</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>ทุกตอนในคิวเคยตรวจ → กดตรวจทั้งคิว → กดยกเลิก</t>
+          <t>ทุกตอนในคิวเคยตรวจ → กดตรวจทั้งคิว</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>ขึ้น "ทุกตอนในคิวตรวจไว้แล้ว" ไม่มีการตรวจ</t>
+          <t>หน้าต่างมีแค่ปุ่ม [ยกเลิก] [ตรวจใหม่ทุกตอน (N)] · กดยกเลิก = ไม่มีอะไรเกิดขึ้น</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -7632,6 +7632,122 @@
       </c>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>SR-09</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>[คิวกลาง] ปิดหน้า / logout</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>สั่งตรวจทั้งคิว แล้วปิดแท็บหรือ logout รอ 5–10 นาที แล้วเปิดหน้าโปรเจกต์ใหม่</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>แผงยังแสดงความคืบหน้าต่อจากเดิม (จำนวนที่ตรวจไปแล้วเพิ่มขึ้น) · ตอนที่ตรวจเสร็จมีป้ายผลตรวจ</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>SR-10</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>[คิวกลาง] เปิดจากเครื่องอื่น</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>ระหว่างตรวจทั้งคิว เปิดหน้าโปรเจกต์เดียวกันจากอีกเครื่อง/เบราว์เซอร์</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>เห็นแผง "ตรวจคำผิด ค้าง N ตอน" และป้ายรอคิวแต่ละตอนเหมือนกัน</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>SR-11</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>[คิวกลาง] ปุ่มตรวจในหน้าเขียนระหว่างคิวยาว</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>ระหว่างตรวจทั้งคิว เปิดตอนที่ไม่อยู่ในคิว กดปุ่ม "ตรวจคำผิด"</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>toast "รอคิวตรวจ ลำดับที่ N" · ตรวจเมื่อถึงคิว แล้วขึ้น "ตรวจเสร็จ…" (อาจใช้เวลานานตามความยาวคิว)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>SR-12</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>[ระบบ] ฟีเจอร์อื่นไม่ค้าง</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>ระหว่างตรวจคำผิด ใช้ฟีเจอร์ที่ใช้ระบบเบื้องหลัง เช่นค้นข้อมูล AI / stylometry</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>ทำงานได้ตามปกติ ไม่ค้างรอการตรวจคำผิด</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -6656,7 +6656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7748,6 +7748,151 @@
       </c>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SM-01</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>[แผงติดตาม] ว่าง</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>เปิดแท็บคิวแก้ไขตอนไม่มีงานตรวจ</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้น "⏸ ระบบตรวจคำผิดว่าง" และปุ่ม "ตรวจคำผิดทั้งคิว" · ถ้าวันนี้เคยตรวจแล้วมีบรรทัดสถิติ "วันนี้ตรวจแล้ว N ตอน · เฉลี่ย … · GPU ใช้ไป x/300 วิ"</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>SM-02</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>[แผงติดตาม] กำลังตรวจ</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>สั่งตรวจทั้งคิว แล้วดูแผง</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้นโหมด (⚡ GPU หรือ CPU) · "กำลังตรวจ: ชื่อตอน · ส่วนที่ i/n · เวลาที่ใช้" พร้อมแถบความคืบหน้าที่ขยับตามส่วน · "รอคิว N ตอน · เหลือราว M นาที" · ตัวเลขอัปเดตเองทุก ~5 วิ</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>SM-03</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>[GPU] โหมดเร่งความเร็ว</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>ตรวจตอนแรกของวัน (ยังมีโควต้า GPU)</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>แผงขึ้น "⚡ โหมดเร่งความเร็ว (GPU)" · ตรวจเสร็จเร็วกว่าเดิมชัดเจน (เดิม ~2 นาที/ตอน) · สถิติ GPU ใช้ไปเพิ่มขึ้น</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>SM-04</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>[GPU] โควต้าหมด</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>ตรวจหลายตอนจนโควต้า GPU วันนี้หมด</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>ไม่มี error · แผงเปลี่ยนเป็น "โหมดปกติ (CPU)" + "โควต้า GPU วันนี้หมด · ลองเร่งความเร็วอีกครั้ง HH:MM" · ตรวจต่อจนครบ (ช้าลง)</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>SM-05</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>[แผงติดตาม] งานของโปรเจกต์อื่น</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>ระหว่างที่มีงานตรวจของอีกโปรเจกต์/ผู้ใช้อื่น เปิดคิวแก้ไขของโปรเจกต์นี้</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้น "กำลังตรวจ: ตอนจากโปรเจกต์อื่น" · "รอคิว N ตอน (ของโปรเจกต์นี้ K)" · ไม่เห็นชื่อตอนของคนอื่น · ปุ่มหยุดถอนได้เฉพาะของโปรเจกต์นี้</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -6656,7 +6656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7893,6 +7893,296 @@
       </c>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>RQ-01</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>[คิว] แบ่งกลุ่ม</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>เปิดแท็บคิวแก้ไขที่มีตอนหลายสถานะ</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้นเป็นกลุ่ม "กำลังตรวจคำผิด / ตรวจเสร็จ รอดูผล / รอ Rewrite" พร้อมจำนวน · บรรทัดบนสรุปจำนวนแต่ละกลุ่ม · กลุ่มที่ไม่มีตอนไม่แสดง · กดหัวกลุ่มแล้วพับ/กางได้</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n"/>
+      <c r="G43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>RQ-02</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>[คิว] เรียงลำดับ</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>ดูลำดับตอนในกลุ่ม</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>ตอนที่มีคำผิดค้างเยอะอยู่บน · ที่จำนวนเท่ากันเรียงตามลำดับบทแล้วตามลำดับตอน</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>RQ-03</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>[คิว] แบ่งหน้า</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>กลุ่มที่มีมากกว่า 10 ตอน (เช่นรอ Rewrite 31 ตอน)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>แสดงทีละ 10 ตอน · ท้ายกลุ่มมี "1–10 จาก 31" และปุ่ม ‹ › · หน้าแรกกด ‹ ไม่ได้ หน้าสุดท้ายกด › ไม่ได้</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>RQ-04</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>[คิว] ตรวจที่เลือก</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>ติ๊ก 3 ตอน → กด "ตรวจที่เลือก (3)"</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>ถ้ามีตอนที่เคยตรวจ ขึ้นหน้าต่างให้เลือก "เฉพาะที่ยังไม่ตรวจ" หรือ "ตรวจใหม่ทั้งหมดที่เลือก" · ส่งเข้าคิว toast "ส่ง N ตอนเข้าคิวตรวจแล้ว" · ป้ายตอนเหล่านั้นเปลี่ยนเป็นรอคิว/กำลังตรวจ · ที่เลือกถูกล้าง</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>RQ-05</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>[คิว] เลือกทั้งกลุ่ม</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>ติ๊ก checkbox ที่หัวกลุ่ม</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>เลือกทุกตอนในกลุ่ม (ทุกหน้า) ยกเว้นตอนว่าง · ติ๊กออก = ยกเลิกทั้งกลุ่ม</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>RQ-06</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>[คิว] ตอนว่าง</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>มีตอน 0 คำในคิว</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>แถวจาง ๆ มีป้าย "ว่าง" · checkbox กดไม่ได้ · ไม่มีปุ่มตรวจใหม่</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>RQ-07</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>[คิว] ป้ายสถานะตรวจ</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>ดูแถวรอ Rewrite</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>ยังไม่เคยตรวจ = "ยังไม่ตรวจคำผิด" · มีจุดค้าง = "N จุดคำผิดค้าง" · ตรวจแล้วแก้หมด = "ตรวจแล้ว · ไม่พบคำผิด"</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>RQ-08</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>[คิว] ตรวจใหม่รายตอน</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>กด "ตรวจใหม่" ในแถวที่เคยตรวจ</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>toast "ส่ง … เข้าคิวตรวจใหม่แล้ว" · ป้ายแถวนั้นเปลี่ยนเป็นรอคิว/กำลังตรวจ แล้วกลับมาเป็นผลใหม่</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>RQ-09</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>[คิว] วันที่ภาษาไทย</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>ดูบรรทัดแก้ไขล่าสุด</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>รูปแบบ "แก้ไขล่าสุด 5 ส.ค. 69 · 10:10" (ภาษาไทย ไม่ใช่ Aug 5, 2026)</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>RQ-10</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>[คอลัมน์ซ้าย] เปลี่ยนตามแท็บ</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>สลับแท็บ บท ↔ คิวแก้ไข</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>แท็บบท: เป้าหมาย/ความคืบหน้า/กิจกรรม 14 วัน/เครื่องมือ AI (ไม่มีแผงตรวจคำผิด) · แท็บคิวแก้ไข: แผงตรวจคำผิดอย่างเดียว · ชื่อโปรเจกต์ด้านบนอยู่ทั้งสองแท็บ</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -27,6 +27,7 @@
     <sheet name="เลนบนกระดาน v2.8.0" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="เส้นเชื่อมสีล้วน v2.10.0" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="ตรวจคำผิด v2.12.0" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="ปมเชิงลึก (ใหม่)" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ผู้ช่วย AI (ใหม่)'!$A$1:$G$19</definedName>
@@ -546,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -741,6 +742,16 @@
         <is>
           <t>24</t>
         </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>ปมเชิงลึก (ใหม่)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -8189,6 +8200,704 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>หัวข้อ</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>เงื่อนไข / ขั้นตอน</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>ผลที่คาดหวัง</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>ความสำคัญ</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>ผลทดสอบ</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PT-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>[รายละเอียด] เปิด/ปิด</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>เปิดสมุดปม กดลูกศรหน้าชื่อปม แล้วกดอีกครั้ง</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>กดครั้งแรกกางแผงคำอธิบาย/ประเด็น/อยู่ใต้ปม/ความสัมพันธ์ · ลูกศรหมุนลง · กดซ้ำย่อกลับ</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>PT-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>[คำอธิบาย] บันทึก</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>กางปม พิมพ์ในช่อง "ปมนี้คืออะไร" แล้วคลิกนอกช่อง → ปิดสมุดแล้วเปิดใหม่</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ข้อความยังอยู่ · ตอนย่อปมเห็นตัวอย่างคำอธิบาย 2 บรรทัดใต้ชื่อ</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>PT-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>[คำอธิบาย] ไม่แก้ไม่บันทึก</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>คลิกเข้า-ออกช่องคำอธิบายโดยไม่พิมพ์อะไร</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ไม่มี toast error · ไม่มีการโหลดซ้ำที่สังเกตได้</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>PT-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>[ประเด็น] เพิ่ม</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>พิมพ์ประเด็นแล้วกด Enter (และอีกข้อกดปุ่ม +)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ประเด็นขึ้นเรียงตามลำดับที่เพิ่ม · ช่องว่างลง · หัวปมขึ้น "ประเด็น 0/2"</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PT-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>[ประเด็น] ช่องว่าง</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>กด Enter ตอนช่องว่าง หรือมีแต่เว้นวรรค</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ไม่เพิ่มประเด็น · ปุ่ม + กดไม่ได้</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>PT-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>[ประเด็น] ติ๊กคลี่แล้ว</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>กดวงกลมหน้าประเด็น แล้วกดซ้ำ</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>กดครั้งแรก: ไอคอนติ๊กเขียว ข้อความขีดฆ่า ตัวนับเป็น 1/2 · กดซ้ำกลับเป็นเปิด</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PT-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>[ประเด็น] ลบ</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>ชี้ที่ประเด็นที่มีฉากเลือกไว้ กด X</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>ประเด็นหาย · ฉากที่เคยเลือกประเด็นนั้นกลับเป็น "— ประเด็น —" ไม่ error</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>PT-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>[ฉาก] เลือกประเด็น</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>กางปมที่มีประเด็นและผูกฉากแล้ว เลือกประเด็นในดรอปดาวน์ข้างฉาก แล้วย่อปม</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>ตอนย่อ ชื่อฉากต่อท้ายด้วย " · &lt;ประเด็น&gt;" · ปมที่ไม่มีประเด็นไม่โชว์ดรอปดาวน์</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>PT-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>[ความตึง] ให้คะแนน</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>กดจุดที่ 3 ข้างฉาก แล้วกดจุดที่ 3 ซ้ำ</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>กดแรก: จุด 1-3 เป็นสีส้ม · กดซ้ำ: ล้างเป็นเทาหมด</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>PT-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>[ความตึง] เส้นกราฟ</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>ให้คะแนนอย่างน้อย 2 ฉากในปมเดียว</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>เส้นกราฟเล็กโผล่ใต้หัวปม ขึ้นลงตามคะแนน · มีคะแนนฉากเดียวไม่โชว์เส้น</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>PT-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>[เตือน] ความตึงไม่เพิ่ม</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>ปมที่ฉากบทต้นได้ 4 และฉากบทหลังได้ 2 (ฉากต้องผูกบทแล้ว)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้นป้าย "ความตึงไม่เพิ่มขึ้น" (สีเทา) · ปรับฉากหลังเป็น 5 แล้วป้ายหาย</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>PT-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>[ปมแม่] ตั้ง</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>ปม B เลือก "อยู่ใต้ปม" = A</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>B ย้ายไปอยู่ใต้ A ย่อหน้าเยื้องและมีไอคอนต้นไม้</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>PT-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>[ปมแม่] กันวน</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>หลังทำ PT-12 กางปม A เปิดดรอปดาวน์ "อยู่ใต้ปม"</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>ไม่มี A เอง และไม่มี B (ลูกของ A) ให้เลือก</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>PT-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>[ปมแม่] ลบแม่</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>ลบปม A ที่มี B เป็นลูก</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>B ยังอยู่ ขึ้นมาเป็นปมระดับบน ไม่เยื้อง</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>PT-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>[ความสัมพันธ์] ต้องเฉลยก่อน</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>ปม A เพิ่มความสัมพันธ์ "ต้องเฉลยก่อน" B · ใส่ฉากเฉลยของ B ที่บท 3 · ยังไม่ให้ A เฉลย</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>A ขึ้นป้ายส้ม "ต้องเฉลยก่อน "B" แต่ช้ากว่า" · ปุ่มสมุดปมนับเตือนเพิ่ม</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>PT-16</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>[ความสัมพันธ์] ลำดับถูก</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>ต่อจาก PT-15 ใส่ฉากเฉลยของ A ที่บท 2 (หรือบทเดียวกับ B)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>ป้ายเตือนลำดับหาย</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>PT-17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>[ความสัมพันธ์] ปมหลอก</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>ปม D "เป็นปมหลอกของ" B · B เฉลยแล้ว · D ยังไม่เฉลย</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>D ขึ้น "ปมหลอกยังไม่คลี่ ทั้งที่ "B" เฉลยแล้ว" · ตั้งสถานะ D เป็น "ตั้งใจทิ้ง" แล้วป้ายหาย</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>PT-18</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>[ความสัมพันธ์] ซ้ำ/ลบ</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>เพิ่มความสัมพันธ์เดิมซ้ำ แล้วกด X ลบ</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>ไม่เกิดแถวซ้ำ ไม่ error · ลบแล้วแถวหาย</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>PT-19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>[เตือน] เฉลยแต่ประเด็นค้าง</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>ปมที่มีประเด็นเปิดอยู่ 1 ข้อ ตั้งสถานะ "เฉลยแล้ว"</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้น "เฉลยแล้ว แต่ประเด็นค้าง 1 ข้อ" · ติ๊กประเด็นแล้วป้ายหาย</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>PT-20</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>[ของเดิม] ปมเก่า</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>เปิดปมที่สร้างก่อนรอบนี้</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>แสดงปกติ คำอธิบาย/ประเด็นว่าง ไม่มีคำเตือนใหม่ผุดขึ้นเอง · เตือนเดิม (ยังไม่เฉลย/ไม่ถูกแตะ) ยังทำงาน</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>PT-21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>[ของเดิม] ผูกปมจากการ์ด</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>บน playground ผูกปมกับการ์ด และสร้างปมใหม่จากการ์ด</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>ทำงานเหมือนเดิม ไม่ error · ปมใหม่โผล่ในสมุดปม</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>PT-22</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>[ข้อจำกัด] ลบแล้วย้อนกลับ</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>ลบปมที่มีคำอธิบาย/ประเด็น แล้วกด "ย้อนกลับ" ใน toast</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>ปมกลับมาพร้อมฉากที่ผูก แต่คำอธิบาย/ประเด็น/ความสัมพันธ์/ความตึงหาย (ข้อจำกัดที่รู้แล้ว task.md ข้อ 18)</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -8206,7 +8206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8892,6 +8892,441 @@
       </c>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>PT-23</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>[layout] สองช่อง</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>เปิดแท็บปมเรื่องบนจอคอม</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>ซ้าย = รายการปม (สร้างปมอยู่บนสุด) · ขวา = รายละเอียดปมแรกที่มีเตือน (ไม่มีเตือน = ปมแรก) · สองฝั่งเลื่อนแยกกัน</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>PT-24</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>[layout] เลือกปม + URL</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>กดปมอื่นในรายการ แล้วกดย้อนกลับของเบราว์เซอร์</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>URL มี &amp;thread=&lt;id&gt; · ฝั่งขวาเปลี่ยนเป็นปมนั้น แถวในรายการไฮไลต์ · ย้อนกลับได้ปมก่อนหน้า</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>PT-25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>[layout] คำอธิบายไม่ค้าง</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>พิมพ์คำอธิบายปม A ค้างไว้ (ยังไม่คลิกออก) แล้วกดปม B</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>ฝั่งขวาแสดงคำอธิบายของ B ไม่ใช่ข้อความที่พิมพ์ใน A</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>PT-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>[layout] มือถือ</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>ย่อจอแคบกว่า ~1024px (หรือเปิดบนมือถือ) แล้วกดปม จากนั้นกด "← ปมทั้งหมด"</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>เห็นรายการอย่างเดียว · กดปมแล้วเห็นรายละเอียดอย่างเดียว · ปุ่มกลับพาไปรายการ</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>PT-27</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>[layout] สร้างปม</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>พิมพ์ชื่อในช่องสร้างปมแล้วกด "สร้าง"</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>ปมใหม่โผล่ในรายการและถูกเลือกทันที ฝั่งขวาแสดงปมนั้น</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>PT-28</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>[layout] ลบปมที่เปิดอยู่</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>กดถังขยะของปมที่กำลังดู</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>ปมหาย หน้าไม่พัง ฝั่งขวาเปลี่ยนไปปมอื่นตามกฎ PT-23 · toast มีปุ่มย้อนกลับ</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>PT-29</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>[ความคืบหน้า] คำนวณเอง</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>ปมใหม่ → ผูกฉากหว่าน → ผูกฉากย้ำ → ผูกฉากเฉลย ดูแถบความคืบหน้าทุกขั้น</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>ยังไม่หว่าน → หว่านแล้ว → กำลังสาน → เฉลยครบ (แถบเติมทีละขั้น) · ในรายการซ้ายแสดงคำเดียวกัน</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>PT-30</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>[ความคืบหน้า] เฉลยบางส่วน</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>ปมที่มีประเด็น 2 ข้อ ติ๊กคลี่ 1 ข้อ (ยังไม่มีฉากเฉลย)</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>ความคืบหน้าเป็น "เฉลยบางส่วน"</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>PT-31</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>[บั๊กเดิม] ลบฉากเฉลย</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>ปมที่มีฉากเฉลย ปลดฉากเฉลยนั้นออก</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>ความคืบหน้าถอยกลับ (ไม่ค้าง "เฉลยครบ") · ขึ้นเตือน "ยังไม่มีการเฉลย"</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>PT-32</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>[เจตนา] พักไว้</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>ปมที่ไม่ถูกแตะเกิน 8 บท ตั้งเจตนาเป็น "พักไว้"</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>ป้าย "ไม่ถูกแตะ N บท" หาย · ไม่นับในตัวเลขเตือนของปุ่มสมุดปม · ในรายการขึ้น "· พักไว้"</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>PT-33</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>[เจตนา] ปลายเปิด / ทิ้ง</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>ปมที่ยังไม่เฉลย ตั้งเจตนาเป็น "ตั้งใจค้าง/ปลายเปิด" แล้วลอง "ทิ้งแล้ว"</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>ทั้งสองแบบไม่เตือนว่ายังไม่เฉลย · "ทิ้งแล้ว" แถวในรายการจางลง และไม่มีป้ายเตือนเลย</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>PT-34</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>[เจตนา] ปมเก่า</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>เปิดปมที่เคยตั้งสถานะไว้ก่อนรอบนี้ (หว่านแล้ว/กำลังสาน/เฉลยแล้ว)</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>เจตนาแสดงเป็น "ดำเนินอยู่" · ปมที่เคยกด "เฉลยแล้ว" แต่ไม่มีฉากเฉลย ขึ้นเตือน "ยังไม่มีการเฉลย" (ตั้งใจ)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>PT-35</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>[บทเป้า] เลยเป้า</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>ปมยังไม่เฉลย ตั้ง "ตั้งใจเฉลยภายในบท" เป็นบทที่ไม่ใช่บทสุดท้ายของเรื่อง</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้นป้ายส้ม "เลยบทที่ตั้งใจเฉลยแล้ว" · เปลี่ยนเป็นบทสุดท้าย หรือ "ไม่กำหนด" ป้ายหาย</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>PT-36</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>[บทเป้า] ลบบท</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>ตั้งบทเป้าแล้วลบบทนั้นทิ้ง</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>ปมไม่พัง บทเป้ากลับเป็น "ไม่กำหนด"</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>PT-37</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>[ที่อื่น] รายงานรายตอน + ribbon</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>ปมที่ตั้ง "ปลายเปิด" และแตะบทที่เปิดรายงานรายตอน / ดูเลนปมบนกระดาน</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>รายงานรายตอนไม่ขึ้น "ปมค้าง" ของปมนี้ · เลนปมไม่ทาบช่วงท้ายว่าค้าง</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -28,6 +28,7 @@
     <sheet name="เส้นเชื่อมสีล้วน v2.10.0" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="ตรวจคำผิด v2.12.0" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="ปมเชิงลึก (ใหม่)" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="เส้นทางปม + AI (ใหม่)" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ผู้ช่วย AI (ใหม่)'!$A$1:$G$19</definedName>
@@ -547,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -752,6 +753,16 @@
       </c>
       <c r="B20" s="10" t="n">
         <v>37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>เส้นทางปม + AI (ใหม่)</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -9333,6 +9344,762 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>หัวข้อ</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>เงื่อนไข / ขั้นตอน</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>ผลที่คาดหวัง</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>ความสำคัญ</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>ผลทดสอบ</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TJ-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>[สรุป] จุดแรก/เฉลย</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>เปิดปมที่ผูกการ์ดหว่านและการ์ดเฉลยไว้แล้ว ดูหัวกล่อง "เส้นทางของปม"</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้น "โผล่ครั้งแรก [บท · ฉาก · C0x] · เฉลยที่ [...] · ระยะ N การ์ด · เงียบนานสุด M การ์ด" ตรงกับตำแหน่งการ์ดจริงบนกระดาน</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TJ-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>[ระยะ] นับการ์ด</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>ปมที่หว่านที่การ์ด C01 ฉาก 1 และย้ำที่ C02 ฉาก 2 (ฉาก 1 มีการ์ด 4 ใบ)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ตัวคั่นระหว่างสองจุดขึ้น "ห่าง 4 การ์ด" · โน้ต (sticky note) ไม่ถูกนับ</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TJ-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>[ระยะ] เรียงตามบท</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>ปมที่มีจุดในบท 3 และบท 1 (ผูกบท 3 ก่อน)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>จุดบท 1 อยู่บน บท 3 อยู่ล่าง · ระยะเป็นบวก</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TJ-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>[ระหว่างนั้น] ปมอื่น</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>ระหว่างสองจุดของปม A มีการ์ดที่ผูกปม B, C</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ใต้ตัวคั่นขึ้นชิป "ปม B · หว่าน" ฯลฯ · ชี้ค้างเห็นชื่อฉาก+รหัสการ์ด</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TJ-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>[ระหว่างนั้น] ป้าย</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ให้ปม B เป็นปมย่อยของ A และ C "เป็นปมหลอกของ" A</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ชิป B มีป้าย (ปมย่อย) สีฟ้า · ชิป C มีป้าย (ปมหลอกของปมนี้) สีม่วง · ปมไม่เกี่ยวไม่มีป้าย</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TJ-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>[ระหว่างนั้น] เยอะ</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>ช่วงที่มีปมอื่นเกิน 5 จุด</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>แสดง 5 ชิปแรก + ปุ่ม "+N" กดแล้วเห็นทั้งหมด</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n"/>
+      <c r="G7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TJ-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>[จุดพิเศษ] ทั้งฉาก</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>ผูกปมกับฉากผ่านสมุดปม (ไม่เลือกการ์ด)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>จุดนั้นขึ้นป้าย "ทั้งฉาก" · ระยะนับจากการ์ดแรกของฉาก</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TJ-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>[จุดพิเศษ] ฉากไม่ผูกบท</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ผูกปมกับการ์ดในฉากที่ไม่มีบท</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>จุดนั้นอยู่ท้ายเส้น ป้าย "ไม่ระบุบท" · ตัวคั่นขึ้น "ไม่ทราบระยะ"</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TJ-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>[จุดพิเศษ] การ์ดถูกลบ</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>ลบการ์ดที่ผูกปมบนกระดาน แล้วกลับมาดูปม</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>หน้าไม่พัง · จุดนั้นกลายเป็น "ทั้งฉาก"</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TJ-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>[เบาะแส] นับรายประเด็น</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>ปมมีประเด็น 2 ข้อ · จุดหว่านเลือกประเด็นที่ 1 · มีการ์ดเฉลย</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>กล่อง "เบาะแสก่อนเฉลย" ประเด็น 1 = 1 การ์ด, ประเด็น 2 = 0 การ์ด (สีส้ม)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TJ-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>[เบาะแส] ไม่ยุติธรรม</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>ต่อจาก TJ-10 ติ๊กประเด็น 2 ว่าคลี่แล้ว</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้นเตือน ""ประเด็น 2" เฉลยโดยไม่มีเบาะแสมาก่อน" · เลือกประเด็น 2 ให้จุดหว่านแล้วเตือนหาย</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TJ-12</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>[เบาะแส] ไม่มีประเด็น</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>ปมที่ไม่มีประเด็นเลย</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>แสดงแถวเดียว "ทั้งปม (ยังไม่แบ่งประเด็น)" นับทุกจุดก่อนเฉลย</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TJ-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>[AI] ไฟล์ส่งออกฉาก</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>บนกระดานฉากที่มีปมผ่าน กดส่งออก/คัดลอก Markdown ของฉาก</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>ตารางปมมีคอลัมน์ ความคืบหน้า / เจตนาผู้เขียน / ความตึงในฉากนี้ เป็นคำไทย · มีหัว ปม "...": คืออะไร + ประเด็น ([x]/[ ]) + "← ฉากนี้ขยับประเด็นนี้"</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TJ-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>[AI] สรุปฉาก</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>กดสรุปฉาก (AI) ในฉากที่มีปมพร้อมคำอธิบาย</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>สรุปใช้ได้ปกติ ไม่ error · (ถ้าดูได้) เนื้อหาสะท้อนประเด็นของปม</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TJ-15</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>[AI] ปมไม่ผ่านฉาก</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>ปมที่มีคำอธิบายแต่ไม่ผูกฉากนี้ แล้วส่งออก Markdown ของฉากนี้</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>ไม่มีคำอธิบายของปมนั้นใน Markdown (มีแค่ชื่อในหัวข้อ "ปมที่ยังไม่เฉลย" ถ้ายังค้าง)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TF-01</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>[AI ตรวจเฉลย] ไม่มีเฉลย</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>เปิดปมที่ยังไม่มีการ์ดเฉลย</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>ส่วน "ตรวจการเฉลย (AI)" ขึ้น "ต้องผูกการ์ดเฉลยก่อนถึงจะตรวจได้" ไม่มีปุ่ม</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TF-02</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>[AI ตรวจเฉลย] ตรวจครั้งแรก</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>ปมที่มีหว่าน+เฉลย กด "ตรวจการเฉลย" (เช่น "เสียงปริศนาที่พระเอกได้ยิน")</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>ปุ่มขึ้น "กำลังตรวจ…" แล้วได้ป้าย 1 ใน 4 (ชัดเจน/พอดี/หักมุม/เบาะแสไม่พอ) · "ทายต่อ 3 ข้อ ถึงเฉลย N ข้อ" พร้อมคำทาย ✓/✗ · เช็คลิสต์ 3 ข้อ · บรรทัดล่างมี qwen/qwen3.8-flash · K=3 · เวลา</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TF-03</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>[AI ตรวจเฉลย] ผลถูกเก็บ</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>ต่อจาก TF-02 สลับไปปมอื่นแล้วกลับมา / รีเฟรชหน้า</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>ผลเดิมโผล่ทันทีโดยไม่ต้องกดใหม่ · ไม่มีป้าย "ผลเก่า"</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TF-04</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>[AI ตรวจเฉลย] ผลเก่า</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>แก้เนื้อการ์ดหว่านของปมบนกระดาน แล้วกลับมาดูปม</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้นป้าย "ผลเก่า — การ์ดเปลี่ยนแล้ว"</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n"/>
+      <c r="G20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TF-05</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>[AI ตรวจเฉลย] ไม่เปลี่ยนไม่เรียกซ้ำ</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>กด "ตรวจใหม่" สองครั้งติดกัน</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>ทั้งสองครั้งเรียก AI จริง (ตรวจใหม่บังคับ) · ดู log การใช้ AI ฟีเจอร์ "ตรวจการเฉลยปม" เพิ่มครั้งละ 3 แถว</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TF-06</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>[AI ตรวจเฉลย] ไม่มีคำอธิบาย</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>ปมที่ไม่มีคำอธิบาย กดตรวจ</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>ตรวจได้ · ขึ้นป้าย "ใส่คำอธิบายปมแล้วผลจะแม่นขึ้น"</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TF-07</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>[AI ตรวจเฉลย] การ์ดเฉลยสั้น</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>ปมที่การ์ดเฉลยมีแค่ชื่อ ไม่มีเนื้อ กดตรวจ</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้นป้าย "การ์ดเฉลยสั้น ผลเชื่อได้น้อย"</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TF-08</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>[AI ตรวจเฉลย] quota/ปิดฟีเจอร์</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>ปิดฟีเจอร์ "ตรวจการเฉลยปม" ในหน้า AI Control แล้วกดตรวจ</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>ขึ้น toast error ไม่พัง ไม่บันทึกผลใหม่</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TF-09</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>[AI ตรวจเฉลย] สมเหตุสมผล</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>ลองกับปมที่ตั้งใจให้เดาง่าย (เบาะแสชัด) เทียบปมที่เฉลยแบบโผล่มาเฉยๆ</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>ปมเดาง่ายมีแนวโน้มได้ "ชัดเจน"/"พอดี" · ปมโผล่เฉยๆ มีแนวโน้มได้ "เบาะแสไม่พอ" (K=3 แกว่งได้ ดูแนวโน้มหลายครั้ง)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -9350,7 +9350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10094,6 +10094,151 @@
       </c>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TG-01</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>[กลุ่ม] เส้นทางรวม</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>ตั้งปม B, C ให้อยู่ใต้ปม A (และ D ใต้ B) แล้วเปิดปม A</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>มีกล่อง "เส้นทางรวมของกลุ่ม · ปมย่อยเฉลยแล้ว x/3" · เลน A บนสุด ตามด้วย B, D (เยื้อง ↳), C · จุดหว่าน/ย้ำเป็นวงกลม เฉลยเป็นเพชร อยู่ตำแหน่งตรงกับลำดับการ์ด</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>TG-02</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>[กลุ่ม] เส้นประ</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>ปมย่อยที่ยังไม่เฉลย</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>เลนนั้นเป็นเส้นประ · ปมที่เฉลยแล้วเป็นเส้นทึบ</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TG-03</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>[กลุ่ม] กดเปิดปมย่อย</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>กดชื่อเลนปมย่อย</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>เปิดรายละเอียดปมย่อยนั้น URL เปลี่ยน ?thread=</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TG-04</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>[กลุ่ม] ปมไม่มีลูก</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>เปิดปมที่ไม่มีปมย่อย</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>ไม่มีกล่องเส้นทางรวมของกลุ่ม</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>ต่ำ</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TG-05</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>[เตือน] ปมใหญ่เฉลยแต่ลูกค้าง</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>ผูกการ์ดเฉลยให้ปม A ขณะที่ D (หลาน) ยังไม่เฉลย</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>A ขึ้นป้าย "เฉลยแล้ว แต่ปมย่อยยังค้าง 1 ปม" · ตัวเลขเตือนบนแท็บเพิ่ม · ตั้ง D เป็น "ทิ้งแล้ว" หรือผูกเฉลยให้ D แล้วป้ายหาย</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>สูง</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test-cases.xlsx
+++ b/test-cases.xlsx
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
@@ -8217,7 +8217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>[ข้อจำกัด] ลบแล้วย้อนกลับ</t>
+          <t>[ย้อนกลับ] ลบแล้วกู้คืน</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ปมกลับมาพร้อมฉากที่ผูก แต่คำอธิบาย/ประเด็น/ความสัมพันธ์/ความตึงหาย (ข้อจำกัดที่รู้แล้ว task.md ข้อ 18)</t>
+          <t>ปมกลับมาครบ: คำอธิบาย ประเด็น (สถานะคลี่เดิม) เจตนา บทเป้า ปมแม่ ปมย่อยกลับมาอยู่ใต้ ความสัมพันธ์ทั้งสองทาง และแต่ละจุดผูกการ์ด/ประเด็น/ความตึงเดิม · ผลตรวจ AI ไม่กลับ (ต้องกดตรวจใหม่)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>ต่ำ</t>
+          <t>สูง</t>
         </is>
       </c>
       <c r="F23" s="2" t="n"/>
@@ -9338,6 +9338,35 @@
       </c>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>PT-38</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>[ย้อนกลับ] กู้ได้บางส่วน</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>ลบปม A (ที่มีความสัมพันธ์กับปม B) → ลบปม B → กด "ย้อนกลับ" ของปม A จากเมนูกู้คืน</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>ปม A กลับมา · ขึ้น toast แดง "กู้คืนได้ไม่ครบ: ความสัมพันธ์" · หน้าไม่พัง</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>กลาง</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
